--- a/Base LEK.xlsx
+++ b/Base LEK.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\Poli junior computador\Challenge LEK\Dados-Desafio-LEK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7403566DC7686CA4/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D53E843-6569-4578-B841-76395163C257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A728968-083A-4F1B-A2C5-E5D2424BC517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{55D91078-2950-4BC0-8BD0-21307BE0D8F7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Açúcar e Etanol" sheetId="2" r:id="rId3"/>
+    <sheet name="Base Geral" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet4" sheetId="6" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId3"/>
+    <sheet name="Market Share" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId5"/>
+    <sheet name="Açúcar e Etanol" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -63,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="144">
   <si>
     <t>Ano</t>
   </si>
@@ -89,7 +92,7 @@
     <t>Demanda (Interna) (1000 t)</t>
   </si>
   <si>
-    <t>Demanda (Global)(1000 t)</t>
+    <t>Demanda (Global) (1000 t)</t>
   </si>
   <si>
     <t>MarketShareProdução (%)</t>
@@ -227,6 +230,9 @@
     <t xml:space="preserve">	168.754</t>
   </si>
   <si>
+    <t>Citros</t>
+  </si>
+  <si>
     <t>Cana</t>
   </si>
   <si>
@@ -236,6 +242,93 @@
     <t>Thousand 60-Kilogram Bags</t>
   </si>
   <si>
+    <t>Market Share Produção</t>
+  </si>
+  <si>
+    <t>Market Share Exportação</t>
+  </si>
+  <si>
+    <t>Café Arábica</t>
+  </si>
+  <si>
+    <t>Cana-de-açúcar</t>
+  </si>
+  <si>
+    <t>Players até 30%</t>
+  </si>
+  <si>
+    <t>Brasil (45%)</t>
+  </si>
+  <si>
+    <t>Russia (20%)</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>EUA (31%)</t>
+  </si>
+  <si>
+    <t>Brasil (66%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Colombia (14,8%)</t>
+  </si>
+  <si>
+    <t>União Europeia (15%)</t>
+  </si>
+  <si>
+    <t>México(15%)</t>
+  </si>
+  <si>
+    <t>Brasil ( 21%)</t>
+  </si>
+  <si>
+    <t>Tailândia (12%)</t>
+  </si>
+  <si>
+    <t>Etiópia (9%)</t>
+  </si>
+  <si>
+    <t>Austrália (13%)</t>
+  </si>
+  <si>
+    <t>Demais(10%)</t>
+  </si>
+  <si>
+    <t>Argentina (17%)</t>
+  </si>
+  <si>
+    <t>India (5%)</t>
+  </si>
+  <si>
+    <t>Demais (32,2%)</t>
+  </si>
+  <si>
+    <t>Canadá (13%)</t>
+  </si>
+  <si>
+    <t>Ucrânia (7%)</t>
+  </si>
+  <si>
+    <t>Demais (83%)</t>
+  </si>
+  <si>
+    <t>EUA (11%)</t>
+  </si>
+  <si>
+    <t>Demais(24%)</t>
+  </si>
+  <si>
+    <t>Matar</t>
+  </si>
+  <si>
+    <t>Demais (28%)</t>
+  </si>
+  <si>
     <t>Açúcar (mil t)</t>
   </si>
   <si>
@@ -405,9 +498,6 @@
   </si>
   <si>
     <t>2020/21</t>
-  </si>
-  <si>
-    <t>Citros</t>
   </si>
 </sst>
 </file>
@@ -417,7 +507,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###.00"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -429,7 +519,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Comic Sans MS"/>
-      <family val="4"/>
     </font>
     <font>
       <b/>
@@ -461,7 +550,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -530,10 +618,28 @@
       <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Consolas"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -564,8 +670,26 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -729,30 +853,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
@@ -787,6 +891,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -794,7 +909,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -924,10 +1039,7 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -954,39 +1066,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -996,10 +1093,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="11" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="11" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="11" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1008,17 +1108,40 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="17" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1029,12 +1152,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{174D7EE8-AC1E-469A-9846-A6D9C3509081}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{53A2EA13-9345-4CE2-853F-C9069A7D803E}"/>
@@ -1369,40 +1495,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC96D1AF-776B-469A-AC4A-756D4DE63FAE}">
-  <dimension ref="A1:AL53"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AL67"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="34" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="16.2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:38" ht="18">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1450,7 +1576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:38" ht="18">
       <c r="A2" s="9" t="s">
         <v>14</v>
       </c>
@@ -1467,17 +1593,17 @@
         <v>164.41</v>
       </c>
       <c r="F2" s="5">
-        <f t="shared" ref="F2:F33" si="0">E2*H2</f>
+        <f>E2*H2</f>
         <v>10933265</v>
       </c>
       <c r="G2" s="5">
-        <f t="shared" ref="G2:G33" si="1">E2*I2</f>
+        <f>E2*I2</f>
         <v>186111955.59</v>
       </c>
-      <c r="H2" s="77">
+      <c r="H2" s="28">
         <v>66500</v>
       </c>
-      <c r="I2" s="81">
+      <c r="I2" s="28">
         <v>1131999</v>
       </c>
       <c r="J2" s="5">
@@ -1504,7 +1630,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" ht="18">
       <c r="A3" s="9" t="s">
         <v>17</v>
       </c>
@@ -1521,17 +1647,17 @@
         <v>170.07</v>
       </c>
       <c r="F3" s="5">
-        <f t="shared" si="0"/>
+        <f>E3*H3</f>
         <v>11564760</v>
       </c>
       <c r="G3" s="5">
-        <f t="shared" si="1"/>
+        <f>E3*I3</f>
         <v>193110743.45999998</v>
       </c>
-      <c r="H3" s="77">
+      <c r="H3" s="28">
         <v>68000</v>
       </c>
-      <c r="I3" s="81">
+      <c r="I3" s="28">
         <v>1135478</v>
       </c>
       <c r="J3" s="5">
@@ -1547,7 +1673,7 @@
         <v>102501</v>
       </c>
       <c r="N3" s="5">
-        <f t="shared" ref="N3:N33" si="2">M3/L3</f>
+        <f t="shared" ref="N3:N33" si="0">M3/L3</f>
         <v>5.5325201057915478</v>
       </c>
       <c r="O3" s="1"/>
@@ -1555,7 +1681,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" ht="18">
       <c r="A4" s="9" t="s">
         <v>19</v>
       </c>
@@ -1572,17 +1698,17 @@
         <v>165.47</v>
       </c>
       <c r="F4" s="5">
-        <f t="shared" si="0"/>
+        <f>E4*H4</f>
         <v>11665635</v>
       </c>
       <c r="G4" s="5">
-        <f t="shared" si="1"/>
+        <f>E4*I4</f>
         <v>190906710.28</v>
       </c>
-      <c r="H4" s="77">
+      <c r="H4" s="28">
         <v>70500</v>
       </c>
-      <c r="I4" s="81">
+      <c r="I4" s="28">
         <v>1153724</v>
       </c>
       <c r="J4" s="5">
@@ -1598,7 +1724,7 @@
         <v>87020</v>
       </c>
       <c r="N4" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.3801278502038556</v>
       </c>
       <c r="O4" s="1"/>
@@ -1642,7 +1768,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="27.6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" ht="28.5">
       <c r="A5" s="9" t="s">
         <v>24</v>
       </c>
@@ -1659,17 +1785,17 @@
         <v>259.55</v>
       </c>
       <c r="F5" s="5">
-        <f t="shared" si="0"/>
+        <f>E5*H5</f>
         <v>18557825</v>
       </c>
       <c r="G5" s="5">
-        <f t="shared" si="1"/>
+        <f>E5*I5</f>
         <v>306864148.15000004</v>
       </c>
-      <c r="H5" s="77">
+      <c r="H5" s="28">
         <v>71500</v>
       </c>
-      <c r="I5" s="81">
+      <c r="I5" s="28">
         <v>1182293</v>
       </c>
       <c r="J5" s="5">
@@ -1685,7 +1811,7 @@
         <v>113272.3</v>
       </c>
       <c r="N5" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>5.24848599984246</v>
       </c>
       <c r="O5" s="1"/>
@@ -1729,7 +1855,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="27.6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" ht="28.5">
       <c r="A6" s="9" t="s">
         <v>25</v>
       </c>
@@ -1746,17 +1872,17 @@
         <v>318.81</v>
       </c>
       <c r="F6" s="5">
-        <f t="shared" si="0"/>
+        <f>E6*H6</f>
         <v>24867180</v>
       </c>
       <c r="G6" s="5">
-        <f t="shared" si="1"/>
+        <f>E6*I6</f>
         <v>372206849.28000003</v>
       </c>
-      <c r="H6" s="77">
+      <c r="H6" s="28">
         <v>78000</v>
       </c>
-      <c r="I6" s="81">
+      <c r="I6" s="28">
         <v>1167488</v>
       </c>
       <c r="J6" s="5">
@@ -1772,7 +1898,7 @@
         <v>131866.1</v>
       </c>
       <c r="N6" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>5.9219352057267578</v>
       </c>
       <c r="O6" s="1"/>
@@ -1809,7 +1935,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="27.6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" ht="28.5">
       <c r="A7" s="9" t="s">
         <v>26</v>
       </c>
@@ -1826,17 +1952,17 @@
         <v>252.66</v>
       </c>
       <c r="F7" s="5">
-        <f t="shared" si="0"/>
+        <f>E7*H7</f>
         <v>21223440</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" si="1"/>
+        <f>E7*I7</f>
         <v>309808407.42000002</v>
       </c>
-      <c r="H7" s="77">
+      <c r="H7" s="28">
         <v>84000</v>
       </c>
-      <c r="I7" s="81">
+      <c r="I7" s="28">
         <v>1226187</v>
       </c>
       <c r="J7" s="5">
@@ -1852,7 +1978,7 @@
         <v>115723.2</v>
       </c>
       <c r="N7" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>5.4953201794999647</v>
       </c>
       <c r="O7" s="1"/>
@@ -1898,7 +2024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="27.6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" ht="28.5">
       <c r="A8" s="9" t="s">
         <v>27</v>
       </c>
@@ -1915,17 +2041,17 @@
         <v>190.6</v>
       </c>
       <c r="F8" s="5">
-        <f t="shared" si="0"/>
+        <f>E8*H8</f>
         <v>17630500</v>
       </c>
       <c r="G8" s="5">
-        <f t="shared" si="1"/>
+        <f>E8*I8</f>
         <v>238135258.79999998</v>
       </c>
-      <c r="H8" s="77">
+      <c r="H8" s="28">
         <v>92500</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="28">
         <v>1249398</v>
       </c>
       <c r="J8" s="5">
@@ -1941,7 +2067,7 @@
         <v>139695.79999999999</v>
       </c>
       <c r="N8" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>6.3912066796294171</v>
       </c>
       <c r="O8" s="1"/>
@@ -1984,8 +2110,8 @@
         <v>World</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="27.6" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:38" ht="28.5">
+      <c r="A9" s="79" t="s">
         <v>28</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -2000,18 +2126,18 @@
       <c r="E9" s="6">
         <v>203.2</v>
       </c>
-      <c r="F9" s="70">
-        <f t="shared" si="0"/>
+      <c r="F9" s="63">
+        <f>E9*H9</f>
         <v>19507200</v>
       </c>
-      <c r="G9" s="70">
-        <f t="shared" si="1"/>
+      <c r="G9" s="63">
+        <f>E9*I9</f>
         <v>261794142.39999998</v>
       </c>
-      <c r="H9" s="77">
+      <c r="H9" s="52">
         <v>96000</v>
       </c>
-      <c r="I9" s="81">
+      <c r="I9" s="52">
         <v>1288357</v>
       </c>
       <c r="J9" s="6">
@@ -2072,7 +2198,7 @@
         <v>58285</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="27.6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" ht="28.5">
       <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
@@ -2083,24 +2209,24 @@
         <v>41500</v>
       </c>
       <c r="D10" s="26">
-        <v>8920</v>
+        <v>3800</v>
       </c>
       <c r="E10" s="5">
         <v>209.93</v>
       </c>
       <c r="F10" s="5">
-        <f t="shared" si="0"/>
-        <v>2498.1670000000004</v>
+        <f>E10*H10</f>
+        <v>2498167</v>
       </c>
       <c r="G10" s="5">
-        <f t="shared" si="1"/>
-        <v>153512.15222000002</v>
-      </c>
-      <c r="H10" s="72">
-        <v>11.9</v>
-      </c>
-      <c r="I10" s="72">
-        <v>731.25400000000002</v>
+        <f>E10*I10</f>
+        <v>153512152.22</v>
+      </c>
+      <c r="H10" s="66">
+        <v>11900</v>
+      </c>
+      <c r="I10" s="66">
+        <v>731254</v>
       </c>
       <c r="J10" s="5">
         <v>0.74367064761547241</v>
@@ -2115,7 +2241,7 @@
         <v>5427.6</v>
       </c>
       <c r="N10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.6574618096357225</v>
       </c>
       <c r="O10" s="1"/>
@@ -2158,7 +2284,7 @@
         <v>53524</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" ht="18">
       <c r="A11" s="9" t="s">
         <v>17</v>
       </c>
@@ -2175,18 +2301,18 @@
         <v>201.69</v>
       </c>
       <c r="F11" s="5">
-        <f t="shared" si="0"/>
-        <v>2400.1109999999999</v>
+        <f>E11*H11</f>
+        <v>2400111</v>
       </c>
       <c r="G11" s="5">
-        <f t="shared" si="1"/>
-        <v>149057.38098000002</v>
-      </c>
-      <c r="H11" s="72">
-        <v>11.9</v>
-      </c>
-      <c r="I11" s="72">
-        <v>739.04200000000003</v>
+        <f>E11*I11</f>
+        <v>149057380.97999999</v>
+      </c>
+      <c r="H11" s="87">
+        <v>11900</v>
+      </c>
+      <c r="I11" s="66">
+        <v>739042</v>
       </c>
       <c r="J11" s="5">
         <v>0.67890763695364731</v>
@@ -2201,7 +2327,7 @@
         <v>5154</v>
       </c>
       <c r="N11" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.527709661598823</v>
       </c>
       <c r="O11" s="1"/>
@@ -2212,7 +2338,7 @@
         <v>64033</v>
       </c>
     </row>
-    <row r="12" spans="1:38" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" ht="18">
       <c r="A12" s="9" t="s">
         <v>19</v>
       </c>
@@ -2229,18 +2355,18 @@
         <v>231.57</v>
       </c>
       <c r="F12" s="5">
-        <f t="shared" si="0"/>
-        <v>2732.5260000000003</v>
+        <f>E12*H12</f>
+        <v>2732526</v>
       </c>
       <c r="G12" s="5">
-        <f t="shared" si="1"/>
-        <v>179824.06250999999</v>
-      </c>
-      <c r="H12" s="72">
-        <v>11.8</v>
-      </c>
-      <c r="I12" s="72">
-        <v>776.54300000000001</v>
+        <f>E12*I12</f>
+        <v>179824062.50999999</v>
+      </c>
+      <c r="H12" s="87">
+        <v>11800</v>
+      </c>
+      <c r="I12" s="66">
+        <v>776543</v>
       </c>
       <c r="J12" s="5">
         <v>0.80684922466124631</v>
@@ -2255,7 +2381,7 @@
         <v>6814</v>
       </c>
       <c r="N12" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.9269759450171819</v>
       </c>
       <c r="O12" s="1"/>
@@ -2266,7 +2392,7 @@
         <v>64664</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" ht="18">
       <c r="A13" s="9" t="s">
         <v>24</v>
       </c>
@@ -2283,18 +2409,18 @@
         <v>315.24</v>
       </c>
       <c r="F13" s="5">
-        <f t="shared" si="0"/>
-        <v>3704.07</v>
+        <f>E13*H13</f>
+        <v>3704070</v>
       </c>
       <c r="G13" s="5">
-        <f t="shared" si="1"/>
-        <v>248295.31836</v>
-      </c>
-      <c r="H13" s="72">
-        <v>11.75</v>
-      </c>
-      <c r="I13" s="72">
-        <v>787.63900000000001</v>
+        <f>E13*I13</f>
+        <v>248295318.36000001</v>
+      </c>
+      <c r="H13" s="87">
+        <v>11750</v>
+      </c>
+      <c r="I13" s="66">
+        <v>787639</v>
       </c>
       <c r="J13" s="5">
         <v>0.98345329269229775</v>
@@ -2309,7 +2435,7 @@
         <v>9365.9</v>
       </c>
       <c r="N13" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>3.0911581240304957</v>
       </c>
       <c r="O13" s="1"/>
@@ -2323,7 +2449,7 @@
         <v>62008</v>
       </c>
     </row>
-    <row r="14" spans="1:38" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" ht="18">
       <c r="A14" s="9" t="s">
         <v>25</v>
       </c>
@@ -2340,18 +2466,18 @@
         <v>429.97</v>
       </c>
       <c r="F14" s="5">
-        <f t="shared" si="0"/>
-        <v>5095.1445000000003</v>
+        <f>E14*H14</f>
+        <v>5095144.5</v>
       </c>
       <c r="G14" s="5">
-        <f t="shared" si="1"/>
-        <v>336227.51063000003</v>
-      </c>
-      <c r="H14" s="72">
-        <v>11.85</v>
-      </c>
-      <c r="I14" s="72">
-        <v>781.97900000000004</v>
+        <f>E14*I14</f>
+        <v>336227510.63</v>
+      </c>
+      <c r="H14" s="87">
+        <v>11850</v>
+      </c>
+      <c r="I14" s="66">
+        <v>781979</v>
       </c>
       <c r="J14" s="5">
         <v>1.3351465890761884</v>
@@ -2366,7 +2492,7 @@
         <v>10817.5</v>
       </c>
       <c r="N14" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>3.1350528908853788</v>
       </c>
       <c r="O14" s="1"/>
@@ -2377,7 +2503,7 @@
         <v>62937</v>
       </c>
     </row>
-    <row r="15" spans="1:38" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" ht="18">
       <c r="A15" s="9" t="s">
         <v>26</v>
       </c>
@@ -2394,18 +2520,18 @@
         <v>340.43</v>
       </c>
       <c r="F15" s="5">
-        <f t="shared" si="0"/>
-        <v>4085.16</v>
+        <f>E15*H15</f>
+        <v>4085160</v>
       </c>
       <c r="G15" s="5">
-        <f t="shared" si="1"/>
-        <v>271519.81896999996</v>
-      </c>
-      <c r="H15" s="72">
-        <v>12</v>
-      </c>
-      <c r="I15" s="72">
-        <v>797.57899999999995</v>
+        <f>E15*I15</f>
+        <v>271519818.97000003</v>
+      </c>
+      <c r="H15" s="87">
+        <v>12000</v>
+      </c>
+      <c r="I15" s="66">
+        <v>797579</v>
       </c>
       <c r="J15" s="5">
         <v>1.0229542494229538</v>
@@ -2420,7 +2546,7 @@
         <v>8807.2999999999993</v>
       </c>
       <c r="N15" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.8699491657977054</v>
       </c>
       <c r="O15" s="1"/>
@@ -2431,7 +2557,7 @@
         <v>63388</v>
       </c>
     </row>
-    <row r="16" spans="1:38" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:38" ht="18">
       <c r="A16" s="9" t="s">
         <v>27</v>
       </c>
@@ -2448,18 +2574,18 @@
         <v>268.67</v>
       </c>
       <c r="F16" s="5">
-        <f t="shared" si="0"/>
-        <v>3277.7739999999999</v>
+        <f>E16*H16</f>
+        <v>3277774</v>
       </c>
       <c r="G16" s="5">
-        <f t="shared" si="1"/>
-        <v>215062.27490000002</v>
-      </c>
-      <c r="H16" s="72">
-        <v>12.2</v>
-      </c>
-      <c r="I16" s="72">
-        <v>800.47</v>
+        <f>E16*I16</f>
+        <v>215062274.90000001</v>
+      </c>
+      <c r="H16" s="87">
+        <v>12200</v>
+      </c>
+      <c r="I16" s="66">
+        <v>800470</v>
       </c>
       <c r="J16" s="5">
         <v>0.98695404139477161</v>
@@ -2474,7 +2600,7 @@
         <v>7536.1</v>
       </c>
       <c r="N16" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>3.0772151898734177</v>
       </c>
       <c r="O16" s="1"/>
@@ -2488,8 +2614,8 @@
         <v>66001</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:29" ht="18">
+      <c r="A17" s="79" t="s">
         <v>28</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -2504,24 +2630,24 @@
       <c r="E17" s="6">
         <v>243.33</v>
       </c>
-      <c r="F17" s="70">
-        <f t="shared" si="0"/>
-        <v>3005.1255000000001</v>
-      </c>
-      <c r="G17" s="70">
-        <f t="shared" si="1"/>
-        <v>198523.70045999999</v>
-      </c>
-      <c r="H17" s="73">
-        <v>12.35</v>
-      </c>
-      <c r="I17" s="73">
-        <v>815.86199999999997</v>
-      </c>
-      <c r="J17" s="70">
+      <c r="F17" s="63">
+        <f>E17*H17</f>
+        <v>3005125.5</v>
+      </c>
+      <c r="G17" s="63">
+        <f>E17*I17</f>
+        <v>198523700.46000001</v>
+      </c>
+      <c r="H17" s="87">
+        <v>12350</v>
+      </c>
+      <c r="I17" s="67">
+        <v>815862</v>
+      </c>
+      <c r="J17" s="63">
         <v>0.93265193946113978</v>
       </c>
-      <c r="K17" s="70">
+      <c r="K17" s="63">
         <v>0.94644901343957599</v>
       </c>
       <c r="L17" s="11">
@@ -2531,7 +2657,7 @@
         <v>6616.2</v>
       </c>
       <c r="N17" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.979196685878962</v>
       </c>
       <c r="O17" s="1" t="s">
@@ -2571,7 +2697,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:29" ht="18">
       <c r="A18" s="9" t="s">
         <v>14</v>
       </c>
@@ -2588,38 +2714,38 @@
         <v>2930</v>
       </c>
       <c r="F18" s="5">
-        <f t="shared" si="0"/>
+        <f>E18*H18</f>
         <v>1930959.7622313674</v>
       </c>
       <c r="G18" s="5">
-        <f t="shared" si="1"/>
+        <f>E18*I18</f>
         <v>13765162.94295839</v>
       </c>
       <c r="H18" s="28">
-        <f t="shared" ref="H18:H25" si="3">V18*Y18*0.06</f>
+        <f>V18*Y18*0.06</f>
         <v>659.03063557384553</v>
       </c>
       <c r="I18" s="28">
-        <f t="shared" ref="I18:I25" si="4">U18*Y18*0.06</f>
+        <f>U18*Y18*0.06</f>
         <v>4698.0078303612254</v>
       </c>
       <c r="J18" s="5">
-        <f t="shared" ref="J18:J25" si="5">O18/T18*100</f>
+        <f>O18/T18*100</f>
         <v>47.34415485444292</v>
       </c>
       <c r="K18" s="5">
-        <f t="shared" ref="K18:K25" si="6">X18/W18*100</f>
+        <f>X18/W18*100</f>
         <v>28.991531947652039</v>
       </c>
       <c r="L18" s="7">
         <v>1449.8019999999999</v>
       </c>
       <c r="M18" s="5">
-        <f t="shared" ref="M18:M24" si="7">O18*60/1000</f>
+        <f>O18*60/1000</f>
         <v>2982</v>
       </c>
       <c r="N18" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.0568325881741094</v>
       </c>
       <c r="O18" s="27">
@@ -2642,14 +2768,14 @@
         <v>41426</v>
       </c>
       <c r="Y18">
-        <f t="shared" ref="Y18:Y25" si="8">O18/T18</f>
+        <f>O18/T18</f>
         <v>0.47344154854442921</v>
       </c>
       <c r="AC18" s="16">
         <v>280</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:29" ht="18">
       <c r="A19" s="9" t="s">
         <v>17</v>
       </c>
@@ -2666,38 +2792,38 @@
         <v>2880</v>
       </c>
       <c r="F19" s="5">
-        <f t="shared" si="0"/>
+        <f>E19*H19</f>
         <v>1757643.8649337518</v>
       </c>
       <c r="G19" s="5">
-        <f t="shared" si="1"/>
+        <f>E19*I19</f>
         <v>12366034.352158066</v>
       </c>
       <c r="H19" s="28">
-        <f t="shared" si="3"/>
+        <f>V19*Y19*0.06</f>
         <v>610.29300865755272</v>
       </c>
       <c r="I19" s="28">
-        <f t="shared" si="4"/>
+        <f>U19*Y19*0.06</f>
         <v>4293.761927832662</v>
       </c>
       <c r="J19" s="5">
-        <f t="shared" si="5"/>
+        <f>O19/T19*100</f>
         <v>44.235670802350811</v>
       </c>
       <c r="K19" s="5">
-        <f t="shared" si="6"/>
+        <f>X19/W19*100</f>
         <v>29.050811497355145</v>
       </c>
       <c r="L19" s="7">
         <v>1513.27336279057</v>
       </c>
       <c r="M19" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="M19:M25" si="1">O19*60/1000</f>
         <v>2520</v>
       </c>
       <c r="N19" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.6652642291627757</v>
       </c>
       <c r="O19" s="27">
@@ -2719,14 +2845,14 @@
         <v>40256</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="8"/>
+        <f>O19/T19</f>
         <v>0.44235670802350807</v>
       </c>
       <c r="AC19" s="15">
         <v>280</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:29" ht="18">
       <c r="A20" s="9" t="s">
         <v>19</v>
       </c>
@@ -2743,38 +2869,38 @@
         <v>3320</v>
       </c>
       <c r="F20" s="5">
-        <f t="shared" si="0"/>
+        <f>E20*H20</f>
         <v>2323187.3612369136</v>
       </c>
       <c r="G20" s="5">
-        <f t="shared" si="1"/>
+        <f>E20*I20</f>
         <v>16881272.039264422</v>
       </c>
       <c r="H20" s="28">
-        <f t="shared" si="3"/>
+        <f>V20*Y20*0.06</f>
         <v>699.75522928822693</v>
       </c>
       <c r="I20" s="28">
-        <f t="shared" si="4"/>
+        <f>U20*Y20*0.06</f>
         <v>5084.7204937543438</v>
       </c>
       <c r="J20" s="5">
-        <f t="shared" si="5"/>
+        <f>O20/T20*100</f>
         <v>52.345543782781789</v>
       </c>
       <c r="K20" s="5">
-        <f t="shared" si="6"/>
+        <f>X20/W20*100</f>
         <v>31.639650872817953</v>
       </c>
       <c r="L20" s="7">
         <v>1433.1714999999999</v>
       </c>
       <c r="M20" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2982</v>
       </c>
       <c r="N20" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.0807000418303043</v>
       </c>
       <c r="O20" s="27">
@@ -2796,14 +2922,14 @@
         <v>45675</v>
       </c>
       <c r="Y20">
-        <f t="shared" si="8"/>
+        <f>O20/T20</f>
         <v>0.52345543782781789</v>
       </c>
       <c r="AC20" s="16">
         <v>390</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:29" ht="18">
       <c r="A21" s="9" t="s">
         <v>24</v>
       </c>
@@ -2820,38 +2946,38 @@
         <v>4510</v>
       </c>
       <c r="F21" s="5">
-        <f t="shared" si="0"/>
+        <f>E21*H21</f>
         <v>2526673.0080722016</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="1"/>
+        <f>E21*I21</f>
         <v>18908539.548278194</v>
       </c>
       <c r="H21" s="28">
-        <f t="shared" si="3"/>
+        <f>V21*Y21*0.06</f>
         <v>560.2379175326389</v>
       </c>
       <c r="I21" s="28">
-        <f t="shared" si="4"/>
+        <f>U21*Y21*0.06</f>
         <v>4192.5808311038127</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" si="5"/>
+        <f>O21/T21*100</f>
         <v>41.796323301450236</v>
       </c>
       <c r="K21" s="5">
-        <f t="shared" si="6"/>
+        <f>X21/W21*100</f>
         <v>27.57089858133363</v>
       </c>
       <c r="L21" s="7">
         <v>1452.5773999999999</v>
       </c>
       <c r="M21" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2184</v>
       </c>
       <c r="N21" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.503534338342315</v>
       </c>
       <c r="O21" s="27">
@@ -2879,14 +3005,14 @@
         <v>39685</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="8"/>
+        <f>O21/T21</f>
         <v>0.41796323301450239</v>
       </c>
       <c r="AC21" s="15">
         <v>410</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:29" ht="18">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -2903,38 +3029,38 @@
         <v>5630</v>
       </c>
       <c r="F22" s="5">
-        <f t="shared" si="0"/>
+        <f>E22*H22</f>
         <v>3438338.607703086</v>
       </c>
       <c r="G22" s="5">
-        <f t="shared" si="1"/>
+        <f>E22*I22</f>
         <v>25845585.452308532</v>
       </c>
       <c r="H22" s="28">
-        <f t="shared" si="3"/>
+        <f>V22*Y22*0.06</f>
         <v>610.71733706981991</v>
       </c>
       <c r="I22" s="28">
-        <f t="shared" si="4"/>
+        <f>U22*Y22*0.06</f>
         <v>4590.6901336249612</v>
       </c>
       <c r="J22" s="5">
-        <f t="shared" si="5"/>
+        <f>O22/T22*100</f>
         <v>45.339074763906453</v>
       </c>
       <c r="K22" s="5">
-        <f t="shared" si="6"/>
+        <f>X22/W22*100</f>
         <v>25.19429826089987</v>
       </c>
       <c r="L22" s="7">
         <v>1485.9659999999999</v>
       </c>
       <c r="M22" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2388</v>
       </c>
       <c r="N22" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.607035423421532</v>
       </c>
       <c r="O22" s="27">
@@ -2962,14 +3088,14 @@
         <v>36145</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="8"/>
+        <f>O22/T22</f>
         <v>0.45339074763906451</v>
       </c>
       <c r="AC22" s="16">
         <v>520</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:29" ht="18">
       <c r="A23" s="9" t="s">
         <v>26</v>
       </c>
@@ -2986,38 +3112,38 @@
         <v>4540</v>
       </c>
       <c r="F23" s="5">
-        <f t="shared" si="0"/>
+        <f>E23*H23</f>
         <v>2787264.9280131627</v>
       </c>
       <c r="G23" s="5">
-        <f t="shared" si="1"/>
+        <f>E23*I23</f>
         <v>20623748.001645412</v>
       </c>
       <c r="H23" s="28">
-        <f t="shared" si="3"/>
+        <f>V23*Y23*0.06</f>
         <v>613.9350061703002</v>
       </c>
       <c r="I23" s="28">
-        <f t="shared" si="4"/>
+        <f>U23*Y23*0.06</f>
         <v>4542.675771287536</v>
       </c>
       <c r="J23" s="5">
-        <f t="shared" si="5"/>
+        <f>O23/T23*100</f>
         <v>46.174413821472641</v>
       </c>
       <c r="K23" s="5">
-        <f t="shared" si="6"/>
+        <f>X23/W23*100</f>
         <v>31.722228630753257</v>
       </c>
       <c r="L23" s="7">
         <v>1508.7439999999999</v>
       </c>
       <c r="M23" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2694</v>
       </c>
       <c r="N23" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.7855911937346562</v>
       </c>
       <c r="O23" s="27">
@@ -3045,14 +3171,14 @@
         <v>46750</v>
       </c>
       <c r="Y23">
-        <f t="shared" si="8"/>
+        <f>O23/T23</f>
         <v>0.46174413821472643</v>
       </c>
       <c r="AC23" s="15">
         <v>450</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:29" ht="18">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -3069,38 +3195,38 @@
         <v>5620</v>
       </c>
       <c r="F24" s="5">
-        <f t="shared" si="0"/>
+        <f>E24*H24</f>
         <v>3253041.2861890364</v>
       </c>
       <c r="G24" s="5">
-        <f t="shared" si="1"/>
+        <f>E24*I24</f>
         <v>25401854.842669379</v>
       </c>
       <c r="H24" s="28">
-        <f t="shared" si="3"/>
+        <f>V24*Y24*0.06</f>
         <v>578.83296907278225</v>
       </c>
       <c r="I24" s="28">
-        <f t="shared" si="4"/>
+        <f>U24*Y24*0.06</f>
         <v>4519.9029969162593</v>
       </c>
       <c r="J24" s="5">
-        <f t="shared" si="5"/>
+        <f>O24/T24*100</f>
         <v>43.910860952266901</v>
       </c>
       <c r="K24" s="5">
-        <f t="shared" si="6"/>
+        <f>X24/W24*100</f>
         <v>30.127985026896383</v>
       </c>
       <c r="L24" s="7">
         <v>1486.837</v>
       </c>
       <c r="M24" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2640</v>
       </c>
       <c r="N24" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.7755813179252333</v>
       </c>
       <c r="O24" s="27">
@@ -3128,21 +3254,21 @@
         <v>44750</v>
       </c>
       <c r="Y24">
-        <f t="shared" si="8"/>
+        <f>O24/T24</f>
         <v>0.439108609522669</v>
       </c>
       <c r="AC24" s="16">
         <v>370</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="s">
+    <row r="25" spans="1:29" ht="18">
+      <c r="A25" s="79" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="52">
+      <c r="C25" s="51">
         <v>112400</v>
       </c>
       <c r="D25" s="6">
@@ -3151,39 +3277,39 @@
       <c r="E25" s="6">
         <v>8470</v>
       </c>
-      <c r="F25" s="70">
-        <f t="shared" si="0"/>
+      <c r="F25" s="63">
+        <f>E25*H25</f>
         <v>4504658.4096738733</v>
       </c>
-      <c r="G25" s="70">
-        <f t="shared" si="1"/>
+      <c r="G25" s="63">
+        <f>E25*I25</f>
         <v>35150084.104067422</v>
       </c>
-      <c r="H25" s="53">
-        <f t="shared" si="3"/>
+      <c r="H25" s="52">
+        <f>V25*Y25*0.06</f>
         <v>531.83688425901687</v>
       </c>
-      <c r="I25" s="53">
-        <f t="shared" si="4"/>
+      <c r="I25" s="52">
+        <f>U25*Y25*0.06</f>
         <v>4149.9508977647492</v>
       </c>
-      <c r="J25" s="70">
-        <f t="shared" si="5"/>
+      <c r="J25" s="63">
+        <f>O25/T25*100</f>
         <v>39.784327069046746</v>
       </c>
-      <c r="K25" s="70">
-        <f t="shared" si="6"/>
+      <c r="K25" s="63">
+        <f>X25/W25*100</f>
         <v>27.149472001065995</v>
       </c>
       <c r="L25" s="8">
         <v>1548.3710000000001</v>
       </c>
-      <c r="M25" s="70">
-        <f t="shared" ref="M25" si="9">O25*60/1000</f>
+      <c r="M25" s="5">
+        <f t="shared" si="1"/>
         <v>2280</v>
       </c>
       <c r="N25" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.472515308023723</v>
       </c>
       <c r="O25" s="27">
@@ -3211,16 +3337,16 @@
         <v>40750</v>
       </c>
       <c r="Y25">
-        <f t="shared" si="8"/>
+        <f>O25/T25</f>
         <v>0.39784327069046749</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:29" ht="18">
       <c r="A26" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="86" t="s">
-        <v>114</v>
+      <c r="B26" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C26" s="28">
         <v>53261.46</v>
@@ -3232,43 +3358,43 @@
         <v>790</v>
       </c>
       <c r="F26" s="5">
-        <f t="shared" si="0"/>
-        <v>41080</v>
+        <f>E26*H26</f>
+        <v>15268330</v>
       </c>
       <c r="G26" s="5">
-        <f t="shared" si="1"/>
-        <v>1336653.9300000002</v>
-      </c>
-      <c r="H26" s="72">
-        <v>52</v>
-      </c>
-      <c r="I26" s="72">
-        <v>1691.9670000000001</v>
-      </c>
-      <c r="J26" s="49">
+        <f>E26*I26</f>
+        <v>23944900</v>
+      </c>
+      <c r="H26" s="66">
+        <v>19327</v>
+      </c>
+      <c r="I26" s="66">
+        <v>30310</v>
+      </c>
+      <c r="J26" s="87">
         <v>63.368201798048794</v>
       </c>
-      <c r="K26" s="49">
+      <c r="K26" s="87">
         <v>69.78871466634763</v>
       </c>
-      <c r="L26" s="5">
-        <v>378.423</v>
+      <c r="L26" s="92">
+        <v>601.5</v>
       </c>
       <c r="M26" s="5">
         <v>11.667999999999999</v>
       </c>
       <c r="N26" s="5">
-        <f t="shared" si="2"/>
-        <v>3.0833221025149102E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.9398171238570239E-2</v>
       </c>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:29" ht="18">
       <c r="A27" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="86" t="s">
-        <v>114</v>
+      <c r="B27" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C27" s="28">
         <v>49630.31</v>
@@ -3280,43 +3406,43 @@
         <v>560</v>
       </c>
       <c r="F27" s="5">
-        <f t="shared" si="0"/>
-        <v>35280</v>
+        <f>E27*H27</f>
+        <v>8338960</v>
       </c>
       <c r="G27" s="5">
-        <f t="shared" si="1"/>
-        <v>943008.64</v>
-      </c>
-      <c r="H27" s="72">
-        <v>63</v>
-      </c>
-      <c r="I27" s="72">
-        <v>1683.944</v>
-      </c>
-      <c r="J27" s="49">
+        <f>E27*I27</f>
+        <v>16478000</v>
+      </c>
+      <c r="H27" s="66">
+        <v>14891</v>
+      </c>
+      <c r="I27" s="66">
+        <v>29425</v>
+      </c>
+      <c r="J27" s="87">
         <v>63.829541100984734</v>
       </c>
-      <c r="K27" s="49">
+      <c r="K27" s="87">
         <v>72.674316643961788</v>
       </c>
-      <c r="L27" s="5">
-        <v>370.048</v>
+      <c r="L27" s="92">
+        <v>595.79999999999995</v>
       </c>
       <c r="M27" s="5">
         <v>15.781000000000001</v>
       </c>
       <c r="N27" s="5">
-        <f t="shared" si="2"/>
-        <v>4.2645818920788656E-2</v>
+        <f t="shared" si="0"/>
+        <v>2.6487076200067138E-2</v>
       </c>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:29" ht="18">
       <c r="A28" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="86" t="s">
-        <v>114</v>
+      <c r="B28" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C28" s="28">
         <v>55314.48</v>
@@ -3328,43 +3454,43 @@
         <v>600</v>
       </c>
       <c r="F28" s="5">
-        <f t="shared" si="0"/>
-        <v>42000</v>
+        <f>E28*H28</f>
+        <v>8820000</v>
       </c>
       <c r="G28" s="5">
-        <f t="shared" si="1"/>
-        <v>989119.79999999993</v>
-      </c>
-      <c r="H28" s="72">
-        <v>70</v>
-      </c>
-      <c r="I28" s="72">
-        <v>1648.5329999999999</v>
-      </c>
-      <c r="J28" s="49">
+        <f>E28*I28</f>
+        <v>18069600</v>
+      </c>
+      <c r="H28" s="66">
+        <v>14700</v>
+      </c>
+      <c r="I28" s="66">
+        <v>30116</v>
+      </c>
+      <c r="J28" s="87">
         <v>60.545499558094818</v>
       </c>
-      <c r="K28" s="49">
+      <c r="K28" s="87">
         <v>68.972487489346818</v>
       </c>
-      <c r="L28" s="5">
-        <v>364.44400000000002</v>
+      <c r="L28" s="92">
+        <v>595.70000000000005</v>
       </c>
       <c r="M28" s="5">
         <v>10.96</v>
       </c>
       <c r="N28" s="5">
-        <f t="shared" si="2"/>
-        <v>3.0073207406350496E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.8398522746348834E-2</v>
       </c>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:29" ht="18">
       <c r="A29" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="86" t="s">
-        <v>114</v>
+      <c r="B29" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C29" s="28">
         <v>52971.88</v>
@@ -3376,43 +3502,43 @@
         <v>650</v>
       </c>
       <c r="F29" s="5">
-        <f t="shared" si="0"/>
-        <v>47450</v>
+        <f>E29*H29</f>
+        <v>11024000</v>
       </c>
       <c r="G29" s="5">
-        <f t="shared" si="1"/>
-        <v>1038792.9500000001</v>
-      </c>
-      <c r="H29" s="72">
-        <v>73</v>
-      </c>
-      <c r="I29" s="72">
-        <v>1598.143</v>
-      </c>
-      <c r="J29" s="49">
+        <f>E29*I29</f>
+        <v>20044050</v>
+      </c>
+      <c r="H29" s="66">
+        <v>16960</v>
+      </c>
+      <c r="I29" s="66">
+        <v>30837</v>
+      </c>
+      <c r="J29" s="87">
         <v>67.22432252986151</v>
       </c>
-      <c r="K29" s="49">
+      <c r="K29" s="87">
         <v>71.099938686288837</v>
       </c>
-      <c r="L29" s="5">
-        <v>346.01299999999998</v>
+      <c r="L29" s="92">
+        <v>604.4</v>
       </c>
       <c r="M29" s="5">
         <v>10.728999999999999</v>
       </c>
       <c r="N29" s="5">
-        <f t="shared" si="2"/>
-        <v>3.1007505498348329E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.7751489080079418E-2</v>
       </c>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:29" ht="18">
       <c r="A30" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="86" t="s">
-        <v>114</v>
+      <c r="B30" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C30" s="28">
         <v>85401.25</v>
@@ -3424,43 +3550,43 @@
         <v>920</v>
       </c>
       <c r="F30" s="5">
-        <f t="shared" si="0"/>
-        <v>69000</v>
+        <f>E30*H30</f>
+        <v>14268280</v>
       </c>
       <c r="G30" s="5">
-        <f t="shared" si="1"/>
-        <v>1341742.72</v>
-      </c>
-      <c r="H30" s="72">
-        <v>75</v>
-      </c>
-      <c r="I30" s="72">
-        <v>1458.4159999999999</v>
-      </c>
-      <c r="J30" s="49">
+        <f>E30*I30</f>
+        <v>27862200</v>
+      </c>
+      <c r="H30" s="66">
+        <v>15509</v>
+      </c>
+      <c r="I30" s="66">
+        <v>30285</v>
+      </c>
+      <c r="J30" s="87">
         <v>74.843103662080722</v>
       </c>
-      <c r="K30" s="49">
+      <c r="K30" s="87">
         <v>73.694159938124756</v>
       </c>
-      <c r="L30" s="5">
-        <v>344.38900000000001</v>
+      <c r="L30" s="92">
+        <v>600</v>
       </c>
       <c r="M30" s="5">
         <v>12.82</v>
       </c>
       <c r="N30" s="5">
-        <f t="shared" si="2"/>
-        <v>3.7225346918745954E-2</v>
+        <f t="shared" si="0"/>
+        <v>2.1366666666666666E-2</v>
       </c>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:29" ht="18">
       <c r="A31" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="86" t="s">
-        <v>114</v>
+      <c r="B31" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C31" s="28">
         <v>98218.85</v>
@@ -3472,43 +3598,43 @@
         <v>1570</v>
       </c>
       <c r="F31" s="5">
-        <f t="shared" si="0"/>
-        <v>86350</v>
+        <f>E31*H31</f>
+        <v>19395780</v>
       </c>
       <c r="G31" s="5">
-        <f t="shared" si="1"/>
-        <v>2124388.98</v>
-      </c>
-      <c r="H31" s="72">
-        <v>55</v>
-      </c>
-      <c r="I31" s="72">
-        <v>1353.114</v>
-      </c>
-      <c r="J31" s="49">
+        <f>E31*I31</f>
+        <v>46245920</v>
+      </c>
+      <c r="H31" s="66">
+        <v>12354</v>
+      </c>
+      <c r="I31" s="66">
+        <v>29456</v>
+      </c>
+      <c r="J31" s="87">
         <v>66.877148528913338</v>
       </c>
-      <c r="K31" s="49">
+      <c r="K31" s="87">
         <v>68.884462222033093</v>
       </c>
-      <c r="L31" s="5">
-        <v>337.09100000000001</v>
+      <c r="L31" s="92">
+        <v>590</v>
       </c>
       <c r="M31" s="5">
         <v>12.535</v>
       </c>
       <c r="N31" s="5">
-        <f t="shared" si="2"/>
-        <v>3.7185804426697833E-2</v>
+        <f t="shared" si="0"/>
+        <v>2.1245762711864406E-2</v>
       </c>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:29" ht="18">
       <c r="A32" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="86" t="s">
-        <v>114</v>
+      <c r="B32" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C32" s="28">
         <v>96166.67</v>
@@ -3520,400 +3646,418 @@
         <v>2260</v>
       </c>
       <c r="F32" s="5">
-        <f t="shared" si="0"/>
-        <v>131080</v>
+        <f>E32*H32</f>
+        <v>29470400</v>
       </c>
       <c r="G32" s="5">
-        <f t="shared" si="1"/>
-        <v>2540108.92</v>
-      </c>
-      <c r="H32" s="72">
-        <v>58</v>
-      </c>
-      <c r="I32" s="72">
-        <v>1123.942</v>
-      </c>
-      <c r="J32" s="49">
+        <f>E32*I32</f>
+        <v>64712840</v>
+      </c>
+      <c r="H32" s="66">
+        <v>13040</v>
+      </c>
+      <c r="I32" s="66">
+        <v>28634</v>
+      </c>
+      <c r="J32" s="87">
         <v>75.56770533340098</v>
       </c>
-      <c r="K32" s="49">
+      <c r="K32" s="87">
         <v>77.04610294569035</v>
       </c>
-      <c r="L32" s="5">
-        <v>336.267</v>
+      <c r="L32" s="92">
+        <v>590</v>
       </c>
       <c r="M32" s="5">
         <v>9.4190000000000005</v>
       </c>
       <c r="N32" s="5">
-        <f t="shared" si="2"/>
-        <v>2.8010479767565655E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.5964406779661017E-2</v>
       </c>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:31" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A33" s="9" t="s">
+    <row r="33" spans="1:31" ht="18">
+      <c r="A33" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="86" t="s">
-        <v>114</v>
+      <c r="B33" s="63" t="s">
+        <v>54</v>
       </c>
       <c r="C33" s="30">
         <v>111764.79</v>
       </c>
-      <c r="D33" s="53">
+      <c r="D33" s="52">
         <v>43278.86</v>
       </c>
       <c r="E33" s="6">
         <v>1420</v>
       </c>
-      <c r="F33" s="70">
+      <c r="F33" s="63">
+        <f>E33*H33</f>
+        <v>19248100</v>
+      </c>
+      <c r="G33" s="63">
+        <f>E33*I33</f>
+        <v>40431660</v>
+      </c>
+      <c r="H33" s="67">
+        <v>13555</v>
+      </c>
+      <c r="I33" s="67">
+        <v>28473</v>
+      </c>
+      <c r="J33" s="68">
+        <v>76.381161292996396</v>
+      </c>
+      <c r="K33" s="68">
+        <v>76.482579018754521</v>
+      </c>
+      <c r="L33" s="92">
+        <v>590</v>
+      </c>
+      <c r="M33" s="63">
+        <v>11.952</v>
+      </c>
+      <c r="N33" s="6">
         <f t="shared" si="0"/>
-        <v>83780</v>
-      </c>
-      <c r="G33" s="70">
-        <f t="shared" si="1"/>
-        <v>1659116.6400000001</v>
-      </c>
-      <c r="H33" s="73">
-        <v>59</v>
-      </c>
-      <c r="I33" s="73">
-        <v>1168.3920000000001</v>
-      </c>
-      <c r="J33" s="74">
-        <v>76.381161292996396</v>
-      </c>
-      <c r="K33" s="74">
-        <v>76.482579018754521</v>
-      </c>
-      <c r="L33" s="70">
-        <v>362.16</v>
-      </c>
-      <c r="M33" s="70">
-        <v>11.952</v>
-      </c>
-      <c r="N33" s="6">
-        <f t="shared" si="2"/>
-        <v>3.3001988071570572E-2</v>
+        <v>2.0257627118644067E-2</v>
       </c>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:31" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:31" ht="18">
       <c r="A34" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="5">
+        <v>55</v>
+      </c>
+      <c r="C34" s="28">
+        <f>N34*O34</f>
+        <v>940548.07919175399</v>
+      </c>
+      <c r="D34" s="28">
+        <v>361170.55486929556</v>
+      </c>
+      <c r="E34" s="28">
+        <f>F34/M34</f>
+        <v>38.460991744228231</v>
+      </c>
+      <c r="F34" s="28">
+        <v>23862560.528000001</v>
+      </c>
+      <c r="G34" s="28">
+        <f>F34/J34</f>
+        <v>78566999.166340321</v>
+      </c>
+      <c r="H34" s="28">
+        <v>618362.43396637763</v>
+      </c>
+      <c r="I34" s="69">
+        <f>H34/J34</f>
+        <v>2035945.8397989636</v>
+      </c>
+      <c r="J34" s="32">
+        <f>(M34*1000)/'Açúcar e Etanol'!O25</f>
+        <v>0.30372243793451642</v>
+      </c>
+      <c r="K34" s="32">
+        <f>AK9/AL9</f>
+        <v>0.33627863086557436</v>
+      </c>
+      <c r="L34" s="76">
+        <v>8589.2300000000014</v>
+      </c>
+      <c r="M34" s="76">
+        <v>620435.39300000004</v>
+      </c>
+      <c r="N34" s="28">
+        <f t="shared" ref="N34:N41" si="2">M34/L34</f>
+        <v>72.234110973859117</v>
+      </c>
+      <c r="O34" s="28">
         <v>13020.83</v>
       </c>
-      <c r="D34" s="5">
-        <v>5000</v>
-      </c>
-      <c r="E34" s="28">
-        <f t="shared" ref="E34:E41" si="10">F34/M34</f>
-        <v>38.460991744228231</v>
-      </c>
-      <c r="F34" s="5">
-        <v>23862560.528000001</v>
-      </c>
-      <c r="G34" s="5">
-        <f t="shared" ref="G34:G41" si="11">F34/J34</f>
-        <v>785669.99166340323</v>
-      </c>
-      <c r="H34" s="28">
-        <v>631591.76614557183</v>
-      </c>
-      <c r="I34" s="75">
-        <f>H34/J34</f>
-        <v>20795.031491277085</v>
-      </c>
-      <c r="J34">
-        <f>((M34*1000)/'Açúcar e Etanol'!O25)*100</f>
-        <v>30.372243793451641</v>
-      </c>
-      <c r="K34">
-        <f t="shared" ref="K34:K41" si="12">(AK9/AL9)*100</f>
-        <v>33.627863086557433</v>
-      </c>
-      <c r="L34" s="10">
-        <v>8589.2300000000014</v>
-      </c>
-      <c r="M34" s="10">
-        <v>620435.39300000004</v>
-      </c>
-      <c r="N34" s="5">
-        <f t="shared" ref="N34:N41" si="13">M34/L34</f>
-        <v>72.234110973859117</v>
-      </c>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="1:31" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:31" ht="18">
       <c r="A35" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="5">
+        <v>55</v>
+      </c>
+      <c r="C35" s="28">
+        <f>N35*O35</f>
+        <v>1057405.269870609</v>
+      </c>
+      <c r="D35" s="28">
+        <v>411119.13603616192</v>
+      </c>
+      <c r="E35" s="28">
+        <f>F35/M35</f>
+        <v>37.854908908602575</v>
+      </c>
+      <c r="F35" s="28">
+        <v>24330022.713</v>
+      </c>
+      <c r="G35" s="28">
+        <f>F35/J35</f>
+        <v>78437078.689148888</v>
+      </c>
+      <c r="H35" s="28">
+        <v>615882.14211875852</v>
+      </c>
+      <c r="I35" s="69">
+        <f t="shared" ref="I35:I41" si="3">H35/J35</f>
+        <v>1985530.2485516691</v>
+      </c>
+      <c r="J35" s="32">
+        <f>(M35*1000)/'Açúcar e Etanol'!O26</f>
+        <v>0.31018522259633635</v>
+      </c>
+      <c r="K35" s="32">
+        <f t="shared" ref="K35:K41" si="4">AK10/AL10</f>
+        <v>0.36021224123757567</v>
+      </c>
+      <c r="L35" s="76">
+        <v>8442.02</v>
+      </c>
+      <c r="M35" s="76">
+        <v>642717.772</v>
+      </c>
+      <c r="N35" s="28">
+        <f t="shared" si="2"/>
+        <v>76.133173340029984</v>
+      </c>
+      <c r="O35" s="28">
         <v>13888.89</v>
       </c>
-      <c r="D35" s="5">
-        <v>5400</v>
-      </c>
-      <c r="E35" s="28">
-        <f t="shared" si="10"/>
-        <v>37.854908908602575</v>
-      </c>
-      <c r="F35" s="5">
-        <v>24330022.713</v>
-      </c>
-      <c r="G35" s="5">
-        <f t="shared" si="11"/>
-        <v>784370.78689148894</v>
-      </c>
-      <c r="H35" s="28">
-        <v>653732.37821367511</v>
-      </c>
-      <c r="I35" s="75">
-        <f t="shared" ref="I35:I41" si="14">H35/J35</f>
-        <v>21075.548755732263</v>
-      </c>
-      <c r="J35">
-        <f>((M35*1000)/'Açúcar e Etanol'!O26)*100</f>
-        <v>31.018522259633635</v>
-      </c>
-      <c r="K35">
-        <f t="shared" si="12"/>
-        <v>36.02122412375757</v>
-      </c>
-      <c r="L35" s="10">
-        <v>8442.02</v>
-      </c>
-      <c r="M35" s="10">
-        <v>642717.772</v>
-      </c>
-      <c r="N35" s="5">
-        <f t="shared" si="13"/>
-        <v>76.133173340029984</v>
-      </c>
-      <c r="O35" s="1"/>
       <c r="Q35" s="5"/>
       <c r="U35" s="16"/>
       <c r="V35" s="16"/>
     </row>
-    <row r="36" spans="1:31" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:31" ht="18">
       <c r="A36" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="5">
+        <v>55</v>
+      </c>
+      <c r="C36" s="28">
+        <f>N36*O36</f>
+        <v>564924.45141131233</v>
+      </c>
+      <c r="D36" s="28">
+        <v>631874.3796996841</v>
+      </c>
+      <c r="E36" s="28">
+        <f>F36/M36</f>
+        <v>36.264488717136224</v>
+      </c>
+      <c r="F36" s="28">
+        <v>23656266.001999997</v>
+      </c>
+      <c r="G36" s="28">
+        <f>F36/J36</f>
+        <v>72196329.295548841</v>
+      </c>
+      <c r="H36" s="28">
+        <v>614673.82202433178</v>
+      </c>
+      <c r="I36" s="69">
+        <f t="shared" si="3"/>
+        <v>1875917.089386398</v>
+      </c>
+      <c r="J36" s="32">
+        <f>(M36*1000)/'Açúcar e Etanol'!O27</f>
+        <v>0.32766577238516875</v>
+      </c>
+      <c r="K36" s="32">
+        <f t="shared" si="4"/>
+        <v>0.50208486249277717</v>
+      </c>
+      <c r="L36" s="76">
+        <v>8620.26</v>
+      </c>
+      <c r="M36" s="76">
+        <v>652325.92099999997</v>
+      </c>
+      <c r="N36" s="28">
+        <f t="shared" si="2"/>
+        <v>75.673578407147801</v>
+      </c>
+      <c r="O36" s="28">
         <v>7465.28</v>
       </c>
-      <c r="D36" s="5">
-        <v>8350</v>
-      </c>
-      <c r="E36" s="28">
-        <f t="shared" si="10"/>
-        <v>36.264488717136224</v>
-      </c>
-      <c r="F36" s="5">
-        <v>23656266.001999997</v>
-      </c>
-      <c r="G36" s="5">
-        <f t="shared" si="11"/>
-        <v>721963.29295548843</v>
-      </c>
-      <c r="H36" s="28">
-        <v>684939.45397468563</v>
-      </c>
-      <c r="I36" s="75">
-        <f t="shared" si="14"/>
-        <v>20903.600915921859</v>
-      </c>
-      <c r="J36">
-        <f>((M36*1000)/'Açúcar e Etanol'!O27)*100</f>
-        <v>32.766577238516874</v>
-      </c>
-      <c r="K36">
-        <f t="shared" si="12"/>
-        <v>50.208486249277719</v>
-      </c>
-      <c r="L36" s="10">
-        <v>8620.26</v>
-      </c>
-      <c r="M36" s="10">
-        <v>652325.92099999997</v>
-      </c>
-      <c r="N36" s="5">
-        <f t="shared" si="13"/>
-        <v>75.673578407147801</v>
-      </c>
-      <c r="O36" s="1"/>
       <c r="Q36" s="5">
         <f>S36*60/1000</f>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:31" ht="18">
       <c r="A37" s="9" t="s">
         <v>24</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C37" s="28">
+        <f>N37*O37</f>
+        <v>908255.02787994884</v>
+      </c>
+      <c r="D37" s="28">
+        <v>510037.28133377904</v>
+      </c>
+      <c r="E37" s="28">
+        <f>F37/M37</f>
+        <v>52.44427785251569</v>
+      </c>
+      <c r="F37" s="28">
+        <v>30690868.143999998</v>
+      </c>
+      <c r="G37" s="28">
+        <f>F37/J37</f>
+        <v>207917154.86826536</v>
+      </c>
+      <c r="H37" s="28">
+        <v>533706.76204364304</v>
+      </c>
+      <c r="I37" s="69">
+        <f t="shared" si="3"/>
+        <v>3615628.9544309406</v>
+      </c>
+      <c r="J37" s="32">
+        <f>(M37*1000)/'Açúcar e Etanol'!O28</f>
+        <v>0.1476110432707945</v>
+      </c>
+      <c r="K37" s="32">
+        <f t="shared" si="4"/>
+        <v>0.40130520846220463</v>
+      </c>
+      <c r="L37" s="76">
+        <v>8317.989999999998</v>
+      </c>
+      <c r="M37" s="76">
+        <v>585209.09049999993</v>
+      </c>
+      <c r="N37" s="28">
+        <f t="shared" si="2"/>
+        <v>70.354627800706666</v>
+      </c>
+      <c r="O37" s="28">
         <v>12909.67</v>
       </c>
-      <c r="D37" s="28">
-        <v>7249.52</v>
-      </c>
-      <c r="E37" s="28">
-        <f t="shared" si="10"/>
-        <v>52.44427785251569</v>
-      </c>
-      <c r="F37" s="5">
-        <v>30690868.143999998</v>
-      </c>
-      <c r="G37" s="5">
-        <f t="shared" si="11"/>
-        <v>2079171.5486826536</v>
-      </c>
-      <c r="H37" s="28">
-        <v>615465.53093421389</v>
-      </c>
-      <c r="I37" s="75">
-        <f t="shared" si="14"/>
-        <v>41695.087121980017</v>
-      </c>
-      <c r="J37">
-        <f>((M37*1000)/'Açúcar e Etanol'!O28)*100</f>
-        <v>14.761104327079449</v>
-      </c>
-      <c r="K37">
-        <f t="shared" si="12"/>
-        <v>40.130520846220463</v>
-      </c>
-      <c r="L37" s="10">
-        <v>8317.989999999998</v>
-      </c>
-      <c r="M37" s="10">
-        <v>585209.09049999993</v>
-      </c>
-      <c r="N37" s="5">
-        <f t="shared" si="13"/>
-        <v>70.354627800706666</v>
-      </c>
-      <c r="O37" s="1"/>
       <c r="S37" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" ht="18">
       <c r="A38" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C38" s="28">
+        <f>N38*O38</f>
+        <v>1257941.1892193791</v>
+      </c>
+      <c r="D38" s="28">
+        <v>787830.69885101111</v>
+      </c>
+      <c r="E38" s="28">
+        <f>F38/M38</f>
+        <v>55.350532224896256</v>
+      </c>
+      <c r="F38" s="28">
+        <v>33771095.890000001</v>
+      </c>
+      <c r="G38" s="28">
+        <f>F38/J38</f>
+        <v>112088394.94777039</v>
+      </c>
+      <c r="H38" s="28">
+        <v>605679.96761501231</v>
+      </c>
+      <c r="I38" s="69">
+        <f t="shared" si="3"/>
+        <v>2010289.9723217799</v>
+      </c>
+      <c r="J38" s="32">
+        <f>(M38*1000)/'Açúcar e Etanol'!O29</f>
+        <v>0.30128985169014377</v>
+      </c>
+      <c r="K38" s="32">
+        <f t="shared" si="4"/>
+        <v>0.4547800283834344</v>
+      </c>
+      <c r="L38" s="76">
+        <v>8288.8669200000022</v>
+      </c>
+      <c r="M38" s="76">
+        <v>610131.36699000001</v>
+      </c>
+      <c r="N38" s="28">
+        <f t="shared" si="2"/>
+        <v>73.608536954288539</v>
+      </c>
+      <c r="O38" s="28">
         <v>17089.61</v>
       </c>
-      <c r="D38" s="28">
-        <v>10702.98</v>
-      </c>
-      <c r="E38" s="28">
-        <f t="shared" si="10"/>
-        <v>55.350532224896256</v>
-      </c>
-      <c r="F38" s="5">
-        <v>33771095.890000001</v>
-      </c>
-      <c r="G38" s="5">
-        <f t="shared" si="11"/>
-        <v>1120883.9494777038</v>
-      </c>
-      <c r="H38" s="28">
-        <v>680840.78088851331</v>
-      </c>
-      <c r="I38" s="75">
-        <f t="shared" si="14"/>
-        <v>22597.534469521794</v>
-      </c>
-      <c r="J38">
-        <f>((M38*1000)/'Açúcar e Etanol'!O29)*100</f>
-        <v>30.128985169014378</v>
-      </c>
-      <c r="K38">
-        <f t="shared" si="12"/>
-        <v>45.478002838343443</v>
-      </c>
-      <c r="L38" s="10">
-        <v>8288.8669200000022</v>
-      </c>
-      <c r="M38" s="10">
-        <v>610131.36699000001</v>
-      </c>
-      <c r="N38" s="5">
-        <f t="shared" si="13"/>
-        <v>73.608536954288539</v>
-      </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="1:31" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:31" ht="18">
       <c r="A39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C39" s="28">
+        <f>N39*O39</f>
+        <v>1500160.4529399532</v>
+      </c>
+      <c r="D39" s="28">
+        <v>802371.06324354757</v>
+      </c>
+      <c r="E39" s="28">
+        <f>F39/M39</f>
+        <v>56.720920133971049</v>
+      </c>
+      <c r="F39" s="28">
+        <v>40454161.506999999</v>
+      </c>
+      <c r="G39" s="28">
+        <f>F39/J39</f>
+        <v>120387399.35384379</v>
+      </c>
+      <c r="H39" s="28">
+        <v>660290.55747308198</v>
+      </c>
+      <c r="I39" s="69">
+        <f t="shared" si="3"/>
+        <v>1964956.386954884</v>
+      </c>
+      <c r="J39" s="32">
+        <f>(M39*1000)/'Açúcar e Etanol'!O30</f>
+        <v>0.33603318722831399</v>
+      </c>
+      <c r="K39" s="32">
+        <f t="shared" si="4"/>
+        <v>0.57158746047634934</v>
+      </c>
+      <c r="L39" s="76">
+        <v>8333.9285132178193</v>
+      </c>
+      <c r="M39" s="76">
+        <v>713214.12648895604</v>
+      </c>
+      <c r="N39" s="28">
+        <f t="shared" si="2"/>
+        <v>85.579582949119441</v>
+      </c>
+      <c r="O39" s="28">
         <v>17529.419999999998</v>
       </c>
-      <c r="D39" s="28">
-        <v>9375.73</v>
-      </c>
-      <c r="E39" s="28">
-        <f t="shared" si="10"/>
-        <v>56.720920133971049</v>
-      </c>
-      <c r="F39" s="5">
-        <v>40454161.506999999</v>
-      </c>
-      <c r="G39" s="5">
-        <f t="shared" si="11"/>
-        <v>1203873.9935384381</v>
-      </c>
-      <c r="H39" s="28">
-        <v>775285.45707343332</v>
-      </c>
-      <c r="I39" s="75">
-        <f t="shared" si="14"/>
-        <v>23071.693110677021</v>
-      </c>
-      <c r="J39">
-        <f>((M39*1000)/'Açúcar e Etanol'!O30)*100</f>
-        <v>33.603318722831396</v>
-      </c>
-      <c r="K39">
-        <f t="shared" si="12"/>
-        <v>57.158746047634935</v>
-      </c>
-      <c r="L39" s="10">
-        <v>8333.9285132178193</v>
-      </c>
-      <c r="M39" s="10">
-        <v>713214.12648895604</v>
-      </c>
-      <c r="N39" s="5">
-        <f t="shared" si="13"/>
-        <v>85.579582949119441</v>
-      </c>
-      <c r="O39" s="1"/>
       <c r="S39" s="18" t="s">
         <v>21</v>
       </c>
@@ -3952,56 +4096,59 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="28.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:31" ht="28.5">
       <c r="A40" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="5">
+        <v>55</v>
+      </c>
+      <c r="C40" s="28">
+        <f>N40*O40</f>
+        <v>932568.3154485171</v>
+      </c>
+      <c r="D40" s="28">
+        <v>832156.8278517517</v>
+      </c>
+      <c r="E40" s="28">
+        <f>F40/M40</f>
+        <v>52.675257423472679</v>
+      </c>
+      <c r="F40" s="28">
+        <v>36190991.629000001</v>
+      </c>
+      <c r="G40" s="28">
+        <f>F40/J40</f>
+        <v>107207515.34556131</v>
+      </c>
+      <c r="H40" s="28">
+        <v>612546.24545727612</v>
+      </c>
+      <c r="I40" s="70">
+        <f t="shared" si="3"/>
+        <v>1814527.8162841382</v>
+      </c>
+      <c r="J40" s="32">
+        <f>(M40*1000)/'Açúcar e Etanol'!O31</f>
+        <v>0.33757886760406491</v>
+      </c>
+      <c r="K40" s="32">
+        <f t="shared" si="4"/>
+        <v>0.55041963778633185</v>
+      </c>
+      <c r="L40" s="76">
+        <v>8853.8317801002322</v>
+      </c>
+      <c r="M40" s="76">
+        <v>687058.65712338965</v>
+      </c>
+      <c r="N40" s="28">
+        <f t="shared" si="2"/>
+        <v>77.600148070083577</v>
+      </c>
+      <c r="O40" s="28">
         <v>12017.61</v>
       </c>
-      <c r="D40" s="5">
-        <v>10723.65</v>
-      </c>
-      <c r="E40" s="28">
-        <f t="shared" si="10"/>
-        <v>52.675257423472679</v>
-      </c>
-      <c r="F40" s="5">
-        <v>36190991.629000001</v>
-      </c>
-      <c r="G40" s="5">
-        <f t="shared" si="11"/>
-        <v>1072075.1534556132</v>
-      </c>
-      <c r="H40" s="28">
-        <v>778648.20408427413</v>
-      </c>
-      <c r="I40" s="75">
-        <f t="shared" si="14"/>
-        <v>23065.667872241484</v>
-      </c>
-      <c r="J40">
-        <f>((M40*1000)/'Açúcar e Etanol'!O31)*100</f>
-        <v>33.757886760406492</v>
-      </c>
-      <c r="K40">
-        <f t="shared" si="12"/>
-        <v>55.041963778633182</v>
-      </c>
-      <c r="L40" s="10">
-        <v>8853.8317801002322</v>
-      </c>
-      <c r="M40" s="10">
-        <v>687058.65712338965</v>
-      </c>
-      <c r="N40" s="5">
-        <f t="shared" si="13"/>
-        <v>77.600148070083577</v>
-      </c>
-      <c r="O40" s="1"/>
       <c r="S40" s="17" t="s">
         <v>31</v>
       </c>
@@ -4040,55 +4187,58 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="28.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="9" t="s">
+    <row r="41" spans="1:31" ht="28.5">
+      <c r="A41" s="79" t="s">
         <v>28</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="6">
-        <v>1074.06</v>
-      </c>
-      <c r="D41" s="6">
-        <v>8531</v>
-      </c>
-      <c r="E41" s="53">
-        <f t="shared" si="10"/>
+        <v>55</v>
+      </c>
+      <c r="C41" s="28">
+        <f>N41*O41</f>
+        <v>1748096.8245028374</v>
+      </c>
+      <c r="D41" s="52">
+        <v>641430.71689519542</v>
+      </c>
+      <c r="E41" s="52">
+        <f>F41/M41</f>
         <v>52.134415472350739</v>
       </c>
-      <c r="F41" s="70">
+      <c r="F41" s="52">
         <v>35101259.581999995</v>
       </c>
-      <c r="G41" s="70">
-        <f t="shared" si="11"/>
-        <v>1002893.1309142855</v>
+      <c r="G41" s="52">
+        <f>F41/J41</f>
+        <v>100289313.09142856</v>
       </c>
       <c r="H41" s="30">
-        <v>804516.04135161242</v>
-      </c>
-      <c r="I41" s="76">
-        <f t="shared" si="14"/>
-        <v>22986.172610046069</v>
-      </c>
-      <c r="J41">
-        <v>35</v>
-      </c>
-      <c r="K41">
-        <f t="shared" si="12"/>
-        <v>54.090089544097822</v>
-      </c>
-      <c r="L41" s="11">
+        <v>605460.19469125383</v>
+      </c>
+      <c r="I41" s="71">
+        <f t="shared" si="3"/>
+        <v>1729886.2705464396</v>
+      </c>
+      <c r="J41" s="77">
+        <v>0.35</v>
+      </c>
+      <c r="K41" s="77">
+        <f t="shared" si="4"/>
+        <v>0.54090089544097819</v>
+      </c>
+      <c r="L41" s="78">
         <v>8954.6451551279642</v>
       </c>
-      <c r="M41" s="11">
+      <c r="M41" s="78">
         <v>673283.84262053913</v>
       </c>
-      <c r="N41" s="6">
-        <f t="shared" si="13"/>
+      <c r="N41" s="30">
+        <f t="shared" si="2"/>
         <v>75.188221415449007</v>
       </c>
-      <c r="O41" s="1"/>
+      <c r="O41" s="30">
+        <v>23249.61</v>
+      </c>
       <c r="S41" s="14"/>
       <c r="T41" s="14"/>
       <c r="U41" s="14"/>
@@ -4123,7 +4273,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:31" ht="16.5">
       <c r="A42" s="3"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -4139,7 +4289,7 @@
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
     </row>
-    <row r="43" spans="1:31" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:31" ht="16.5">
       <c r="A43" s="3"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -4155,7 +4305,7 @@
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
     </row>
-    <row r="44" spans="1:31" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:31" ht="16.5">
       <c r="A44" s="3"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -4164,38 +4314,38 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:31" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:31" ht="15.75">
       <c r="A45" s="3"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="77">
+      <c r="G45" s="72">
         <v>66500</v>
       </c>
-      <c r="H45" s="77">
+      <c r="H45" s="72">
         <v>68000</v>
       </c>
-      <c r="I45" s="77">
+      <c r="I45" s="72">
         <v>70500</v>
       </c>
-      <c r="J45" s="77">
+      <c r="J45" s="72">
         <v>71500</v>
       </c>
-      <c r="K45" s="77">
+      <c r="K45" s="72">
         <v>78000</v>
       </c>
-      <c r="L45" s="77">
+      <c r="L45" s="72">
         <v>84000</v>
       </c>
-      <c r="M45" s="77">
+      <c r="M45" s="72">
         <v>92500</v>
       </c>
-      <c r="N45" s="77">
+      <c r="N45" s="72">
         <v>96000</v>
       </c>
-      <c r="O45" s="78"/>
+      <c r="O45" s="73"/>
       <c r="S45" s="18" t="s">
         <v>21</v>
       </c>
@@ -4233,7 +4383,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:31">
       <c r="A46" s="3"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -4279,7 +4429,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:31" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:31">
       <c r="A47" s="3"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -4289,7 +4439,7 @@
       <c r="G47" s="1"/>
       <c r="S47" s="14"/>
       <c r="T47" s="14"/>
-      <c r="U47" s="51" t="s">
+      <c r="U47" s="50" t="s">
         <v>35</v>
       </c>
       <c r="V47" s="13">
@@ -4316,47 +4466,47 @@
       <c r="AC47" s="13">
         <v>66001</v>
       </c>
-      <c r="AD47" s="51" t="s">
+      <c r="AD47" s="50" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:31" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:31" ht="15.75">
       <c r="A48" s="3"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-      <c r="G48" s="81">
+      <c r="G48" s="74">
         <v>1131999</v>
       </c>
-      <c r="H48" s="81">
+      <c r="H48" s="74">
         <v>1135478</v>
       </c>
-      <c r="I48" s="81">
+      <c r="I48" s="74">
         <v>1153724</v>
       </c>
-      <c r="J48" s="81">
+      <c r="J48" s="74">
         <v>1182293</v>
       </c>
-      <c r="K48" s="81">
+      <c r="K48" s="74">
         <v>1167488</v>
       </c>
-      <c r="L48" s="81">
+      <c r="L48" s="74">
         <v>1226187</v>
       </c>
-      <c r="M48" s="81">
+      <c r="M48" s="74">
         <v>1249398</v>
       </c>
-      <c r="N48" s="81">
+      <c r="N48" s="74">
         <v>1288357</v>
       </c>
-      <c r="O48" s="82"/>
+      <c r="O48" s="75"/>
       <c r="P48" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="16.5">
       <c r="A49" s="3"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -4365,7 +4515,7 @@
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" ht="16.5">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -4374,7 +4524,7 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" ht="16.5">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -4383,7 +4533,7 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" ht="16.5">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -4392,7 +4542,7 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" ht="16.5">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -4400,6 +4550,65 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
+    </row>
+    <row r="55" spans="1:15" ht="15" customHeight="1">
+      <c r="G55">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="15" customHeight="1">
+      <c r="L59" s="39"/>
+      <c r="M59" s="40"/>
+      <c r="N59" s="40"/>
+      <c r="O59" s="39"/>
+    </row>
+    <row r="60" spans="1:15" ht="15" customHeight="1">
+      <c r="L60" s="41"/>
+      <c r="M60" s="93"/>
+      <c r="N60" s="93"/>
+      <c r="O60" s="41"/>
+    </row>
+    <row r="61" spans="1:15" ht="15" customHeight="1">
+      <c r="L61" s="41"/>
+      <c r="M61" s="93"/>
+      <c r="N61" s="93"/>
+      <c r="O61" s="41"/>
+    </row>
+    <row r="62" spans="1:15" ht="15" customHeight="1">
+      <c r="L62" s="41"/>
+      <c r="M62" s="93"/>
+      <c r="N62" s="93"/>
+      <c r="O62" s="41"/>
+    </row>
+    <row r="63" spans="1:15" ht="15" customHeight="1">
+      <c r="L63" s="41"/>
+      <c r="M63" s="93"/>
+      <c r="N63" s="93"/>
+      <c r="O63" s="41"/>
+    </row>
+    <row r="64" spans="1:15" ht="15" customHeight="1">
+      <c r="L64" s="41"/>
+      <c r="M64" s="93"/>
+      <c r="N64" s="93"/>
+      <c r="O64" s="41"/>
+    </row>
+    <row r="65" spans="12:15" ht="15" customHeight="1">
+      <c r="L65" s="41"/>
+      <c r="M65" s="93"/>
+      <c r="N65" s="93"/>
+      <c r="O65" s="41"/>
+    </row>
+    <row r="66" spans="12:15" ht="15" customHeight="1">
+      <c r="L66" s="41"/>
+      <c r="M66" s="93"/>
+      <c r="N66" s="93"/>
+      <c r="O66" s="41"/>
+    </row>
+    <row r="67" spans="12:15" ht="15" customHeight="1">
+      <c r="L67" s="41"/>
+      <c r="M67" s="93"/>
+      <c r="N67" s="93"/>
+      <c r="O67" s="41"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4412,137 +4621,351 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27695074-3522-43C3-A66F-D328C777B535}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD9E604F-3027-4F44-8D2E-1CC2FDF8AA27}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="15" width="9.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98E5AC7D-67E1-41C1-9541-74E44ACA59D2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3349CB3-9E6F-4431-BFDC-0E0E5FB2BA2E}">
+  <dimension ref="A2:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:13">
+      <c r="B2" s="88" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="H2" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="B3" s="80" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="80" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="80" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="80" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="80" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="B4" s="81">
+        <v>0.42159999999999997</v>
+      </c>
+      <c r="C4" s="82">
+        <v>0.01</v>
+      </c>
+      <c r="D4" s="81">
+        <v>0.28570000000000001</v>
+      </c>
+      <c r="E4" s="81">
+        <v>0.1104</v>
+      </c>
+      <c r="F4" s="81">
+        <v>0.37319999999999998</v>
+      </c>
+      <c r="H4" s="81">
+        <v>0.45</v>
+      </c>
+      <c r="I4" s="81">
+        <v>1.46E-2</v>
+      </c>
+      <c r="J4" s="81">
+        <v>0.75</v>
+      </c>
+      <c r="K4" s="81">
+        <v>0.21</v>
+      </c>
+      <c r="L4" s="81">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L5" t="s">
+        <v>67</v>
+      </c>
+      <c r="M5" s="55"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="G6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K6" t="s">
+        <v>72</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="M6" s="55"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="H7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="H8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I8" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="I9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="E10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="H2:L2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27695074-3522-43C3-A66F-D328C777B535}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F134365-52D9-4BD2-893E-80AC204C292B}">
   <dimension ref="C5:AN54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.109375" customWidth="1"/>
-    <col min="15" max="15" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="33.33203125" customWidth="1"/>
-    <col min="19" max="19" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="56.88671875" customWidth="1"/>
-    <col min="22" max="22" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.140625" customWidth="1"/>
+    <col min="15" max="15" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="33.28515625" customWidth="1"/>
+    <col min="19" max="19" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="56.85546875" customWidth="1"/>
+    <col min="22" max="22" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="36.28515625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="46" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="33.6640625" customWidth="1"/>
-    <col min="26" max="26" width="43.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="51.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="33.6640625" customWidth="1"/>
-    <col min="29" max="29" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="31.44140625" customWidth="1"/>
-    <col min="34" max="34" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="35.109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="41.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="43.44140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="33.7109375" customWidth="1"/>
+    <col min="26" max="26" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="33.7109375" customWidth="1"/>
+    <col min="29" max="29" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="31.42578125" customWidth="1"/>
+    <col min="34" max="34" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:40" x14ac:dyDescent="0.3">
-      <c r="C5" s="49"/>
-      <c r="D5" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="H5" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="I5" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5" s="49" t="s">
-        <v>63</v>
+    <row r="5" spans="3:40">
+      <c r="C5" s="87"/>
+      <c r="D5" s="87" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="87" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="87" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" s="87" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="87" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="87" t="s">
+        <v>93</v>
       </c>
       <c r="K5" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="L5" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="M5" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="N5" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="O5" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="P5" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q5" s="59" t="s">
-        <v>70</v>
-      </c>
-      <c r="R5" s="59" t="s">
-        <v>71</v>
-      </c>
-      <c r="S5" s="59" t="s">
-        <v>72</v>
-      </c>
-      <c r="T5" s="60" t="s">
-        <v>73</v>
+        <v>94</v>
+      </c>
+      <c r="L5" s="87" t="s">
+        <v>95</v>
+      </c>
+      <c r="M5" s="87" t="s">
+        <v>96</v>
+      </c>
+      <c r="N5" s="87" t="s">
+        <v>97</v>
+      </c>
+      <c r="O5" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="P5" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q5" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="R5" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="S5" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="T5" s="59" t="s">
+        <v>103</v>
       </c>
       <c r="U5" s="45" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="V5" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="W5" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="X5" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y5" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z5" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA5" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB5" s="49"/>
-      <c r="AC5" s="49"/>
-      <c r="AF5" s="79" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="3:40" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="W5" s="87" t="s">
+        <v>106</v>
+      </c>
+      <c r="X5" s="87" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y5" s="87" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z5" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA5" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB5" s="87"/>
+      <c r="AC5" s="87"/>
+      <c r="AF5" s="85" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="3:40" ht="15">
       <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
@@ -4553,16 +4976,19 @@
         <v>138.41926680768839</v>
       </c>
       <c r="F6" s="23">
-        <v>9324469</v>
+        <f>9324469*0.976</f>
+        <v>9100681.743999999</v>
       </c>
       <c r="G6" s="23">
-        <v>23027174</v>
+        <f>23027174*0.976</f>
+        <v>22474521.824000001</v>
       </c>
       <c r="H6" s="23">
-        <v>32351643</v>
+        <f>32351643*0.976</f>
+        <v>31575203.568</v>
       </c>
       <c r="I6" s="24">
-        <f>(D6*1000/E6)/Sheet1!M34</f>
+        <f>(D6*1000/E6)/'Base Geral'!M34</f>
         <v>0.33812602759028954</v>
       </c>
       <c r="J6" s="24">
@@ -4585,20 +5011,20 @@
       <c r="O6" s="47">
         <v>10600</v>
       </c>
-      <c r="P6" s="50">
-        <v>19600</v>
-      </c>
-      <c r="Q6" s="63">
-        <v>20730000</v>
-      </c>
-      <c r="R6" s="63">
-        <v>10100000</v>
-      </c>
-      <c r="S6" s="32">
-        <v>614000</v>
-      </c>
-      <c r="T6" s="64">
-        <v>1022000</v>
+      <c r="P6">
+        <v>19129.599999999999</v>
+      </c>
+      <c r="Q6">
+        <v>20232480</v>
+      </c>
+      <c r="R6">
+        <v>9857600</v>
+      </c>
+      <c r="S6">
+        <v>599264</v>
+      </c>
+      <c r="T6">
+        <v>997472</v>
       </c>
       <c r="U6" s="46">
         <f>O6*K6</f>
@@ -4606,35 +5032,35 @@
       </c>
       <c r="V6" s="32">
         <f>P6*K6</f>
-        <v>5488000</v>
+        <v>5356288</v>
       </c>
       <c r="W6" s="32">
         <f>Q6*M6</f>
-        <v>9540298.4100000001</v>
+        <v>9311331.248159999</v>
       </c>
       <c r="X6" s="32">
         <f>S6*M6</f>
-        <v>282573.23800000001</v>
+        <v>275791.48028800002</v>
       </c>
       <c r="Y6" s="32">
         <f>R6*L6</f>
-        <v>5070604</v>
+        <v>4948909.5040000007</v>
       </c>
       <c r="Z6" s="32">
         <f>T6*L6</f>
-        <v>513084.88000000006</v>
-      </c>
-      <c r="AA6" s="65">
+        <v>500770.84288000007</v>
+      </c>
+      <c r="AA6" s="61">
         <f>SUM(U6:Z6)</f>
-        <v>23862560.528000001</v>
-      </c>
-      <c r="AD6" s="85" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE6" s="85"/>
-      <c r="AF6" s="85"/>
-    </row>
-    <row r="7" spans="3:40" x14ac:dyDescent="0.3">
+        <v>23361091.075327996</v>
+      </c>
+      <c r="AD6" s="91" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE6" s="91"/>
+      <c r="AF6" s="91"/>
+    </row>
+    <row r="7" spans="3:40" ht="15">
       <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
@@ -4645,16 +5071,19 @@
         <v>139.28993584141935</v>
       </c>
       <c r="F7" s="23">
-        <v>10116456.5</v>
+        <f>10116456.5*0.934</f>
+        <v>9448770.3710000012</v>
       </c>
       <c r="G7" s="23">
-        <v>23885161.25</v>
+        <f>23885161.25*0.934</f>
+        <v>22308740.607500002</v>
       </c>
       <c r="H7" s="23">
-        <v>34001617.75</v>
+        <f>34001617.75*0.934</f>
+        <v>31757510.978500001</v>
       </c>
       <c r="I7" s="24">
-        <f>(D7*1000/E7)/Sheet1!M35</f>
+        <f>(D7*1000/E7)/'Base Geral'!M35</f>
         <v>0.33282315909103372</v>
       </c>
       <c r="J7" s="24">
@@ -4677,20 +5106,20 @@
       <c r="O7" s="47">
         <v>10650</v>
       </c>
-      <c r="P7" s="50">
-        <v>19280</v>
-      </c>
-      <c r="Q7" s="63">
-        <v>22544000</v>
-      </c>
-      <c r="R7" s="63">
-        <v>10305000</v>
-      </c>
-      <c r="S7" s="32">
-        <v>657000</v>
-      </c>
-      <c r="T7" s="64">
-        <v>1257000</v>
+      <c r="P7" s="84">
+        <v>18007.52</v>
+      </c>
+      <c r="Q7" s="84">
+        <v>21056096</v>
+      </c>
+      <c r="R7" s="84">
+        <v>9624870</v>
+      </c>
+      <c r="S7" s="84">
+        <v>613638</v>
+      </c>
+      <c r="T7" s="84">
+        <v>1174038</v>
       </c>
       <c r="U7" s="46">
         <f t="shared" ref="U7:U13" si="2">O7*K7</f>
@@ -4698,60 +5127,60 @@
       </c>
       <c r="V7" s="32">
         <f t="shared" ref="V7:V13" si="3">P7*K7</f>
-        <v>5398400</v>
+        <v>5042105.6000000006</v>
       </c>
       <c r="W7" s="32">
         <f t="shared" ref="W7:W13" si="4">Q7*M7</f>
-        <v>10004643.952</v>
+        <v>9344337.4511679988</v>
       </c>
       <c r="X7" s="32">
         <f t="shared" ref="X7:X13" si="5">S7*M7</f>
-        <v>291565.43099999998</v>
+        <v>272322.11255399999</v>
       </c>
       <c r="Y7" s="32">
         <f t="shared" ref="Y7:Y13" si="6">R7*L7</f>
-        <v>5038784.3250000002</v>
+        <v>4706224.5595499994</v>
       </c>
       <c r="Z7" s="32">
         <f t="shared" ref="Z7:Z13" si="7">T7*L7</f>
-        <v>614629.005</v>
-      </c>
-      <c r="AA7" s="65">
+        <v>574063.49066999997</v>
+      </c>
+      <c r="AA7" s="61">
         <f t="shared" ref="AA7:AA13" si="8">SUM(U7:Z7)</f>
-        <v>24330022.713</v>
+        <v>22921053.213941995</v>
       </c>
       <c r="AD7" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="AE7" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="AF7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH7" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI7" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ7" s="59" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK7" s="59" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL7" s="59" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM7" s="60" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN7" s="57" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="3:40" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+      <c r="AH7" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI7" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ7" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK7" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="AL7" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM7" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN7" s="64" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="3:40" ht="15">
       <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
@@ -4762,16 +5191,19 @@
         <v>144.08027352373313</v>
       </c>
       <c r="F8" s="23">
-        <v>9321811.9840000011</v>
+        <f>9321811.984*0.885</f>
+        <v>8249803.6058399994</v>
       </c>
       <c r="G8" s="23">
-        <v>20424610.988985896</v>
+        <f>20424610.9889859*0.885</f>
+        <v>18075780.72525252</v>
       </c>
       <c r="H8" s="23">
-        <v>29746422.972985893</v>
+        <f>29746422.9729859*0.885</f>
+        <v>26325584.331092522</v>
       </c>
       <c r="I8" s="24">
-        <f>(D8*1000/E8)/Sheet1!M36</f>
+        <f>(D8*1000/E8)/'Base Geral'!M36</f>
         <v>0.43893482696326402</v>
       </c>
       <c r="J8" s="24">
@@ -4794,20 +5226,20 @@
       <c r="O8" s="47">
         <v>10150</v>
       </c>
-      <c r="P8" s="50">
-        <v>32150</v>
-      </c>
-      <c r="Q8" s="63">
-        <v>19258000</v>
-      </c>
-      <c r="R8" s="63">
-        <v>9670000</v>
-      </c>
-      <c r="S8" s="32">
-        <v>1565000</v>
-      </c>
-      <c r="T8" s="64">
-        <v>1137000</v>
+      <c r="P8" s="84">
+        <v>28452.75</v>
+      </c>
+      <c r="Q8" s="84">
+        <v>17043330</v>
+      </c>
+      <c r="R8" s="84">
+        <v>8557950</v>
+      </c>
+      <c r="S8" s="84">
+        <v>1385025</v>
+      </c>
+      <c r="T8" s="84">
+        <v>1006245</v>
       </c>
       <c r="U8" s="46">
         <f t="shared" si="2"/>
@@ -4815,27 +5247,27 @@
       </c>
       <c r="V8" s="32">
         <f t="shared" si="3"/>
-        <v>9002000</v>
+        <v>7966770</v>
       </c>
       <c r="W8" s="32">
         <f t="shared" si="4"/>
-        <v>6874605.2920000004</v>
+        <v>6084025.6834200006</v>
       </c>
       <c r="X8" s="32">
         <f t="shared" si="5"/>
-        <v>558664.31000000006</v>
+        <v>494417.91435000004</v>
       </c>
       <c r="Y8" s="32">
         <f t="shared" si="6"/>
-        <v>3918284</v>
+        <v>3467681.34</v>
       </c>
       <c r="Z8" s="32">
         <f t="shared" si="7"/>
-        <v>460712.4</v>
-      </c>
-      <c r="AA8" s="65">
+        <v>407730.47399999999</v>
+      </c>
+      <c r="AA8" s="61">
         <f t="shared" si="8"/>
-        <v>23656266.001999997</v>
+        <v>21262625.411770001</v>
       </c>
       <c r="AC8" s="2" t="s">
         <v>14</v>
@@ -4856,32 +5288,32 @@
         <f>(10600)/($E$6/1049.5)</f>
         <v>80369.592012476176</v>
       </c>
-      <c r="AI8" s="32">
-        <f>19600/($E$6/1049.5)</f>
-        <v>148607.92485325783</v>
-      </c>
-      <c r="AJ8" s="32">
-        <f>20730000/(($E$6)*0.5913)</f>
-        <v>253276.48979645397</v>
-      </c>
-      <c r="AK8" s="32">
-        <f>10100000/(($E$6)*0.5665)</f>
-        <v>128802.6846244551</v>
-      </c>
-      <c r="AL8" s="32">
-        <f>614000/(($E$6)*0.5913)</f>
-        <v>7501.7735038602377</v>
-      </c>
-      <c r="AM8" s="32">
-        <f>1022000/(($E$6)*0.5665)</f>
-        <v>13033.301355068625</v>
-      </c>
-      <c r="AN8" s="65">
+      <c r="AI8">
+        <f>19129.6/($E$6/1049.5)</f>
+        <v>145041.33465677963</v>
+      </c>
+      <c r="AJ8">
+        <f>20232480/(($E$6)*0.5913)</f>
+        <v>247197.85404133907</v>
+      </c>
+      <c r="AK8">
+        <f>9857600/(($E$6)*0.5665)</f>
+        <v>125711.42019346818</v>
+      </c>
+      <c r="AL8">
+        <f>599264/(($E$6)*0.5913)</f>
+        <v>7321.7309397675917</v>
+      </c>
+      <c r="AM8">
+        <f>997472/(($E$6)*0.5665)</f>
+        <v>12720.502122546977</v>
+      </c>
+      <c r="AN8" s="61">
         <f>SUM(AH8:AM8)</f>
-        <v>631591.76614557183</v>
-      </c>
-    </row>
-    <row r="9" spans="3:40" x14ac:dyDescent="0.3">
+        <v>618362.43396637763</v>
+      </c>
+    </row>
+    <row r="9" spans="3:40" ht="15">
       <c r="C9" s="2" t="s">
         <v>24</v>
       </c>
@@ -4892,16 +5324,19 @@
         <v>141.60864476251581</v>
       </c>
       <c r="F9" s="23">
-        <v>10604566.59</v>
+        <f>10604566.59*0.85</f>
+        <v>9013881.6014999989</v>
       </c>
       <c r="G9" s="23">
-        <v>16181899.132856632</v>
+        <f>16181899.1328566*0.85</f>
+        <v>13754614.26292811</v>
       </c>
       <c r="H9" s="23">
-        <v>26786465.722856633</v>
+        <f>26786465.7228566*0.85</f>
+        <v>22768495.86442811</v>
       </c>
       <c r="I9" s="24">
-        <f>(D9*1000/E9)/Sheet1!M37</f>
+        <f>(D9*1000/E9)/'Base Geral'!M37</f>
         <v>0.42293814691745929</v>
       </c>
       <c r="J9" s="24">
@@ -4924,20 +5359,20 @@
       <c r="O9" s="47">
         <v>9500</v>
       </c>
-      <c r="P9" s="50">
-        <v>25950</v>
-      </c>
-      <c r="Q9" s="63">
-        <v>16792000</v>
-      </c>
-      <c r="R9" s="63">
-        <v>10616000</v>
-      </c>
-      <c r="S9" s="32">
-        <v>1020000</v>
-      </c>
-      <c r="T9" s="64">
-        <v>616000</v>
+      <c r="P9" s="84">
+        <v>22057.5</v>
+      </c>
+      <c r="Q9" s="84">
+        <v>14273200</v>
+      </c>
+      <c r="R9" s="84">
+        <v>9023600</v>
+      </c>
+      <c r="S9" s="84">
+        <v>867000</v>
+      </c>
+      <c r="T9" s="84">
+        <v>523600</v>
       </c>
       <c r="U9" s="46">
         <f t="shared" si="2"/>
@@ -4945,27 +5380,27 @@
       </c>
       <c r="V9" s="32">
         <f t="shared" si="3"/>
-        <v>10120500</v>
+        <v>8602425</v>
       </c>
       <c r="W9" s="32">
         <f t="shared" si="4"/>
-        <v>9228144.352</v>
+        <v>7843922.6992000006</v>
       </c>
       <c r="X9" s="32">
         <f t="shared" si="5"/>
-        <v>560547.12</v>
+        <v>476465.05200000003</v>
       </c>
       <c r="Y9" s="32">
         <f t="shared" si="6"/>
-        <v>6688568.3360000001</v>
+        <v>5685283.0855999999</v>
       </c>
       <c r="Z9" s="32">
         <f t="shared" si="7"/>
-        <v>388108.33600000001</v>
-      </c>
-      <c r="AA9" s="65">
+        <v>329892.08559999999</v>
+      </c>
+      <c r="AA9" s="61">
         <f t="shared" si="8"/>
-        <v>30690868.143999998</v>
+        <v>26642987.922400001</v>
       </c>
       <c r="AC9" s="2" t="s">
         <v>17</v>
@@ -4986,32 +5421,32 @@
         <f>10650/($E$7/1049.5)</f>
         <v>80243.952533118674</v>
       </c>
-      <c r="AI9" s="32">
-        <f>19280/($E$7/1049.5)</f>
-        <v>145267.92533695098</v>
-      </c>
-      <c r="AJ9" s="32">
-        <f>22544000/(($E$7)*0.5913)</f>
-        <v>273718.00024216477</v>
-      </c>
-      <c r="AK9" s="32">
-        <f>10305000/(($E$7)*0.5665)</f>
-        <v>130595.53942116167</v>
-      </c>
-      <c r="AL9" s="32">
-        <f>657000/(($E$7)*0.5913)</f>
-        <v>7976.9662064896311</v>
-      </c>
-      <c r="AM9" s="32">
-        <f>1257000/(($E$7)*0.5665)</f>
-        <v>15929.994473789444</v>
-      </c>
-      <c r="AN9" s="65">
+      <c r="AI9">
+        <f>18007.52/($E$7/1049.5)</f>
+        <v>135680.24226471223</v>
+      </c>
+      <c r="AJ9">
+        <f>21056096/(($E$7)*0.5913)</f>
+        <v>255652.6122261819</v>
+      </c>
+      <c r="AK9">
+        <f>9624870/(($E$7)*0.5665)</f>
+        <v>121976.23381936499</v>
+      </c>
+      <c r="AL9">
+        <f>613638/(($E$7)*0.5913)</f>
+        <v>7450.4864368613162</v>
+      </c>
+      <c r="AM9">
+        <f>1174038/(($E$7)*0.5665)</f>
+        <v>14878.614838519341</v>
+      </c>
+      <c r="AN9" s="61">
         <f t="shared" ref="AN9:AN15" si="9">SUM(AH9:AM9)</f>
-        <v>653732.37821367511</v>
-      </c>
-    </row>
-    <row r="10" spans="3:40" x14ac:dyDescent="0.3">
+        <v>615882.14211875852</v>
+      </c>
+    </row>
+    <row r="10" spans="3:40" ht="15">
       <c r="C10" s="2" t="s">
         <v>25</v>
       </c>
@@ -5022,16 +5457,19 @@
         <v>133.46127629926346</v>
       </c>
       <c r="F10" s="23">
-        <v>11647168.814508051</v>
+        <f>11647168.8145081*0.876</f>
+        <v>10202919.881509095</v>
       </c>
       <c r="G10" s="23">
-        <v>15718719.58173953</v>
+        <f>15718719.5817395*0.876</f>
+        <v>13769598.353603803</v>
       </c>
       <c r="H10" s="23">
-        <v>27365888.396247581</v>
+        <f>27365888.3962476*0.876</f>
+        <v>23972518.235112898</v>
       </c>
       <c r="I10" s="24">
-        <f>(D10*1000/E10)/Sheet1!M38</f>
+        <f>(D10*1000/E10)/'Base Geral'!M38</f>
         <v>0.45482863848360744</v>
       </c>
       <c r="J10" s="24">
@@ -5054,20 +5492,20 @@
       <c r="O10" s="47">
         <v>9500</v>
       </c>
-      <c r="P10" s="50">
-        <v>28200</v>
-      </c>
-      <c r="Q10" s="63">
-        <v>15529000</v>
-      </c>
-      <c r="R10" s="63">
-        <v>11621000</v>
-      </c>
-      <c r="S10" s="32">
-        <v>1130000</v>
-      </c>
-      <c r="T10" s="64">
-        <v>1480000</v>
+      <c r="P10" s="84">
+        <v>24703.200000000001</v>
+      </c>
+      <c r="Q10" s="84">
+        <v>13603404</v>
+      </c>
+      <c r="R10" s="84">
+        <v>10179996</v>
+      </c>
+      <c r="S10" s="84">
+        <v>989880</v>
+      </c>
+      <c r="T10" s="84">
+        <v>1296480</v>
       </c>
       <c r="U10" s="46">
         <f t="shared" si="2"/>
@@ -5075,27 +5513,27 @@
       </c>
       <c r="V10" s="32">
         <f t="shared" si="3"/>
-        <v>11562000</v>
+        <v>10128312</v>
       </c>
       <c r="W10" s="32">
         <f t="shared" si="4"/>
-        <v>8952049.2170000002</v>
+        <v>7841995.1140919998</v>
       </c>
       <c r="X10" s="32">
         <f t="shared" si="5"/>
-        <v>651414.49</v>
+        <v>570639.09323999996</v>
       </c>
       <c r="Y10" s="32">
         <f t="shared" si="6"/>
-        <v>7726605.3430000003</v>
+        <v>6768506.2804680001</v>
       </c>
       <c r="Z10" s="32">
         <f t="shared" si="7"/>
-        <v>984026.84</v>
-      </c>
-      <c r="AA10" s="65">
+        <v>862007.51184000005</v>
+      </c>
+      <c r="AA10" s="61">
         <f t="shared" si="8"/>
-        <v>33771095.890000001</v>
+        <v>30066459.999640003</v>
       </c>
       <c r="AC10" s="2" t="s">
         <v>19</v>
@@ -5116,32 +5554,32 @@
         <f>10150/($E$8/1049.5)</f>
         <v>73933.958754217078</v>
       </c>
-      <c r="AI10" s="32">
-        <f>32150/($E$8/1049.5)</f>
-        <v>234184.90383724918</v>
-      </c>
-      <c r="AJ10" s="32">
-        <f>19258000/(($E$8)*0.5913)</f>
-        <v>226047.01637068015</v>
-      </c>
-      <c r="AK10" s="32">
-        <f>9670000/(($E$8)*0.5665)</f>
-        <v>118473.72282578981</v>
-      </c>
-      <c r="AL10" s="32">
-        <f>1565000/(($E$8)*0.5913)</f>
-        <v>18369.694704544316</v>
-      </c>
-      <c r="AM10" s="32">
-        <f>1137000/(($E$8)*0.5665)</f>
-        <v>13930.157482205068</v>
-      </c>
-      <c r="AN10" s="65">
+      <c r="AI10">
+        <f>28452.75/($E$8/1049.5)</f>
+        <v>207253.63989596552</v>
+      </c>
+      <c r="AJ10">
+        <f>17043330/(($E$8)*0.5913)</f>
+        <v>200051.60948805194</v>
+      </c>
+      <c r="AK10">
+        <f>8557950/(($E$8)*0.5665)</f>
+        <v>104849.24470082398</v>
+      </c>
+      <c r="AL10">
+        <f>1385025/(($E$8)*0.5913)</f>
+        <v>16257.17981352172</v>
+      </c>
+      <c r="AM10">
+        <f>1006245/(($E$8)*0.5665)</f>
+        <v>12328.189371751485</v>
+      </c>
+      <c r="AN10" s="61">
         <f t="shared" si="9"/>
-        <v>684939.45397468563</v>
-      </c>
-    </row>
-    <row r="11" spans="3:40" x14ac:dyDescent="0.3">
+        <v>614673.82202433178</v>
+      </c>
+    </row>
+    <row r="11" spans="3:40" ht="15">
       <c r="C11" s="2" t="s">
         <v>26</v>
       </c>
@@ -5152,16 +5590,19 @@
         <v>134.55664819915754</v>
       </c>
       <c r="F11" s="23">
-        <v>12049303.487</v>
+        <f>12049303.487*0.836</f>
+        <v>10073217.715132</v>
       </c>
       <c r="G11" s="23">
-        <v>17640240.160999998</v>
+        <f>17640240.161*0.836</f>
+        <v>14747240.774595998</v>
       </c>
       <c r="H11" s="23">
-        <v>29689543.648000002</v>
+        <f>29689543.648*0.836</f>
+        <v>24820458.489727996</v>
       </c>
       <c r="I11" s="24">
-        <f>(D11*1000/E11)/Sheet1!M39</f>
+        <f>(D11*1000/E11)/'Base Geral'!M39</f>
         <v>0.47597994795261117</v>
       </c>
       <c r="J11" s="24">
@@ -5184,20 +5625,20 @@
       <c r="O11" s="47">
         <v>9500</v>
       </c>
-      <c r="P11" s="50">
-        <v>35974</v>
-      </c>
-      <c r="Q11" s="63">
-        <v>18203000</v>
-      </c>
-      <c r="R11" s="63">
-        <v>12201000</v>
-      </c>
-      <c r="S11" s="32">
-        <v>1420000</v>
-      </c>
-      <c r="T11" s="64">
-        <v>1060000</v>
+      <c r="P11" s="84">
+        <v>30074.263999999999</v>
+      </c>
+      <c r="Q11" s="84">
+        <v>15217708</v>
+      </c>
+      <c r="R11" s="84">
+        <v>10200036</v>
+      </c>
+      <c r="S11" s="84">
+        <v>1187120</v>
+      </c>
+      <c r="T11" s="84">
+        <v>886160</v>
       </c>
       <c r="U11" s="46">
         <f t="shared" si="2"/>
@@ -5205,27 +5646,27 @@
       </c>
       <c r="V11" s="32">
         <f t="shared" si="3"/>
-        <v>18706480</v>
+        <v>15638617.279999999</v>
       </c>
       <c r="W11" s="32">
         <f t="shared" si="4"/>
-        <v>8748889.686999999</v>
+        <v>7314071.7783319997</v>
       </c>
       <c r="X11" s="32">
         <f t="shared" si="5"/>
-        <v>682493.17999999993</v>
+        <v>570564.29848</v>
       </c>
       <c r="Y11" s="32">
         <f t="shared" si="6"/>
-        <v>6786684.2399999993</v>
+        <v>5673668.0246399995</v>
       </c>
       <c r="Z11" s="32">
         <f t="shared" si="7"/>
-        <v>589614.39999999991</v>
-      </c>
-      <c r="AA11" s="65">
+        <v>492917.63839999994</v>
+      </c>
+      <c r="AA11" s="61">
         <f t="shared" si="8"/>
-        <v>40454161.506999999</v>
+        <v>34629839.019852005</v>
       </c>
       <c r="AC11" s="2" t="s">
         <v>24</v>
@@ -5246,32 +5687,32 @@
         <f>9500/($E$9/1049.5)</f>
         <v>70407.071663743176</v>
       </c>
-      <c r="AI11" s="32">
-        <f>25950/($E$9/1049.5)</f>
-        <v>192322.47470254058</v>
-      </c>
-      <c r="AJ11" s="32">
-        <f>16792000/(($E$9)*0.5913)</f>
-        <v>200541.74061076678</v>
-      </c>
-      <c r="AK11" s="32">
-        <f>10616000/(($E$9)*0.5665)</f>
-        <v>132333.93578593538</v>
-      </c>
-      <c r="AL11" s="32">
-        <f>1020000/(($E$9)*0.5913)</f>
-        <v>12181.549274832189</v>
-      </c>
-      <c r="AM11" s="32">
-        <f>616000/(($E$9)*0.5665)</f>
-        <v>7678.7588963956468</v>
-      </c>
-      <c r="AN11" s="65">
+      <c r="AI11">
+        <f>22057.5/($E$9/1049.5)</f>
+        <v>163474.10349715949</v>
+      </c>
+      <c r="AJ11">
+        <f>14273200/(($E$9)*0.5913)</f>
+        <v>170460.47951915176</v>
+      </c>
+      <c r="AK11">
+        <f>9023600/(($E$9)*0.5665)</f>
+        <v>112483.84541804506</v>
+      </c>
+      <c r="AL11">
+        <f>867000/(($E$9)*0.5913)</f>
+        <v>10354.31688360736</v>
+      </c>
+      <c r="AM11">
+        <f>523600/(($E$9)*0.5665)</f>
+        <v>6526.9450619362997</v>
+      </c>
+      <c r="AN11" s="61">
         <f t="shared" si="9"/>
-        <v>615465.53093421389</v>
-      </c>
-    </row>
-    <row r="12" spans="3:40" x14ac:dyDescent="0.3">
+        <v>533706.76204364304</v>
+      </c>
+    </row>
+    <row r="12" spans="3:40" ht="15">
       <c r="C12" s="2" t="s">
         <v>27</v>
       </c>
@@ -5282,16 +5723,19 @@
         <v>137.26774810783303</v>
       </c>
       <c r="F12" s="23">
-        <v>10467182.516216589</v>
+        <f>10467182.5162166*0.766</f>
+        <v>8017861.8074219162</v>
       </c>
       <c r="G12" s="23">
-        <v>18868830.543388616</v>
+        <f>18868830.5433886*0.766</f>
+        <v>14453524.19623567</v>
       </c>
       <c r="H12" s="23">
-        <v>29336013.059605211</v>
+        <f>29336013.0596052*0.766</f>
+        <v>22471386.003657583</v>
       </c>
       <c r="I12" s="24">
-        <f>(D12*1000/E12)/Sheet1!M40</f>
+        <f>(D12*1000/E12)/'Base Geral'!M40</f>
         <v>0.47559022770654347</v>
       </c>
       <c r="J12" s="24">
@@ -5314,20 +5758,20 @@
       <c r="O12" s="47">
         <v>9000</v>
       </c>
-      <c r="P12" s="50">
-        <v>34890</v>
-      </c>
-      <c r="Q12" s="63">
-        <v>21665000</v>
-      </c>
-      <c r="R12" s="63">
-        <v>12085000</v>
-      </c>
-      <c r="S12" s="32">
-        <v>1130000</v>
-      </c>
-      <c r="T12" s="64">
-        <v>531000</v>
+      <c r="P12" s="84">
+        <v>26725.74</v>
+      </c>
+      <c r="Q12" s="84">
+        <v>16595390</v>
+      </c>
+      <c r="R12" s="84">
+        <v>9257110</v>
+      </c>
+      <c r="S12" s="84">
+        <v>865580</v>
+      </c>
+      <c r="T12" s="84">
+        <v>406746</v>
       </c>
       <c r="U12" s="46">
         <f t="shared" si="2"/>
@@ -5335,27 +5779,27 @@
       </c>
       <c r="V12" s="32">
         <f t="shared" si="3"/>
-        <v>15700500</v>
+        <v>12026583</v>
       </c>
       <c r="W12" s="32">
         <f t="shared" si="4"/>
-        <v>9614385.375</v>
+        <v>7364619.1972499993</v>
       </c>
       <c r="X12" s="32">
         <f t="shared" si="5"/>
-        <v>501465.75</v>
+        <v>384122.76449999999</v>
       </c>
       <c r="Y12" s="32">
         <f t="shared" si="6"/>
-        <v>6058440.1149999993</v>
+        <v>4640765.1280899998</v>
       </c>
       <c r="Z12" s="32">
         <f t="shared" si="7"/>
-        <v>266200.38899999997</v>
-      </c>
-      <c r="AA12" s="65">
+        <v>203909.49797399997</v>
+      </c>
+      <c r="AA12" s="61">
         <f t="shared" si="8"/>
-        <v>36190991.629000001</v>
+        <v>28669999.587814003</v>
       </c>
       <c r="AC12" s="2" t="s">
         <v>25</v>
@@ -5376,32 +5820,32 @@
         <f>9500/($E$10/1049.5)</f>
         <v>74705.189973183427</v>
       </c>
-      <c r="AI12" s="32">
-        <f>28200/($E$10/1049.5)</f>
-        <v>221756.45865723921</v>
-      </c>
-      <c r="AJ12" s="32">
-        <f>15529000/(($E$10)*0.5913)</f>
-        <v>196779.71952921609</v>
-      </c>
-      <c r="AK12" s="32">
-        <f>11621000/(($E$10)*0.5665)</f>
-        <v>153705.11254713836</v>
-      </c>
-      <c r="AL12" s="32">
-        <f>1130000/(($E$10)*0.5913)</f>
-        <v>14319.085779381428</v>
-      </c>
-      <c r="AM12" s="32">
-        <f>1480000/(($E$10)*0.5665)</f>
-        <v>19575.21440235477</v>
-      </c>
-      <c r="AN12" s="65">
+      <c r="AI12">
+        <f>24703.2/($E$10/1049.5)</f>
+        <v>194258.65778374157</v>
+      </c>
+      <c r="AJ12">
+        <f>13603404/(($E$10)*0.5913)</f>
+        <v>172379.03430759331</v>
+      </c>
+      <c r="AK12">
+        <f>10179996/(($E$10)*0.5665)</f>
+        <v>134645.6785912932</v>
+      </c>
+      <c r="AL12">
+        <f>989880/(($E$10)*0.5913)</f>
+        <v>12543.519142738131</v>
+      </c>
+      <c r="AM12">
+        <f>1296480/(($E$10)*0.5665)</f>
+        <v>17147.887816462779</v>
+      </c>
+      <c r="AN12" s="61">
         <f t="shared" si="9"/>
-        <v>680840.78088851331</v>
-      </c>
-    </row>
-    <row r="13" spans="3:40" x14ac:dyDescent="0.3">
+        <v>605679.96761501231</v>
+      </c>
+    </row>
+    <row r="13" spans="3:40" ht="15">
       <c r="C13" s="2" t="s">
         <v>28</v>
       </c>
@@ -5412,16 +5856,19 @@
         <v>134.94993812352337</v>
       </c>
       <c r="F13" s="23">
-        <v>10119720.200965505</v>
+        <f>10119720.2009655*0.729</f>
+        <v>7377276.0265038488</v>
       </c>
       <c r="G13" s="23">
-        <v>17211219.258266881</v>
+        <f>17211219.2582669*0.729</f>
+        <v>12546978.839276569</v>
       </c>
       <c r="H13" s="23">
-        <v>27330939.45923239</v>
+        <f>27330939.4592324*0.729</f>
+        <v>19924254.865780421</v>
       </c>
       <c r="I13" s="24">
-        <f>(D13*1000/E13)/Sheet1!M41</f>
+        <f>(D13*1000/E13)/'Base Geral'!M41</f>
         <v>0.48623451221371083</v>
       </c>
       <c r="J13" s="24">
@@ -5441,23 +5888,23 @@
         <f t="shared" si="1"/>
         <v>0.52565300000000004</v>
       </c>
-      <c r="O13" s="61">
+      <c r="O13" s="60">
         <v>9000</v>
       </c>
-      <c r="P13" s="62">
-        <v>35700</v>
-      </c>
-      <c r="Q13" s="66">
-        <v>20857000</v>
-      </c>
-      <c r="R13" s="66">
-        <v>13666000</v>
-      </c>
-      <c r="S13" s="67">
-        <v>970000</v>
-      </c>
-      <c r="T13" s="68">
-        <v>351000</v>
+      <c r="P13" s="84">
+        <v>26025.3</v>
+      </c>
+      <c r="Q13" s="84">
+        <v>15204753</v>
+      </c>
+      <c r="R13" s="84">
+        <v>9962514</v>
+      </c>
+      <c r="S13" s="84">
+        <v>707130</v>
+      </c>
+      <c r="T13" s="84">
+        <v>255879</v>
       </c>
       <c r="U13" s="46">
         <f t="shared" si="2"/>
@@ -5465,27 +5912,27 @@
       </c>
       <c r="V13" s="32">
         <f t="shared" si="3"/>
-        <v>13209000</v>
+        <v>9629361</v>
       </c>
       <c r="W13" s="32">
         <f t="shared" si="4"/>
-        <v>10217802.585999999</v>
+        <v>7448778.085194</v>
       </c>
       <c r="X13" s="32">
         <f t="shared" si="5"/>
-        <v>475201.06</v>
+        <v>346421.57273999997</v>
       </c>
       <c r="Y13" s="32">
         <f t="shared" si="6"/>
-        <v>7672201.7280000001</v>
+        <v>5593035.0597120002</v>
       </c>
       <c r="Z13" s="32">
         <f t="shared" si="7"/>
-        <v>197054.20800000001</v>
-      </c>
-      <c r="AA13" s="69">
+        <v>143652.517632</v>
+      </c>
+      <c r="AA13" s="62">
         <f t="shared" si="8"/>
-        <v>35101259.581999995</v>
+        <v>26491248.235277999</v>
       </c>
       <c r="AC13" s="2" t="s">
         <v>26</v>
@@ -5506,32 +5953,32 @@
         <f>9500/($E$11/1049.5)</f>
         <v>74097.044876170039</v>
       </c>
-      <c r="AI13" s="32">
-        <f>35974/($E$11/1049.5)</f>
-        <v>280586.00972372008</v>
-      </c>
-      <c r="AJ13" s="32">
-        <f>18203000/(($E$11)*0.5913)</f>
-        <v>228786.25518916798</v>
-      </c>
-      <c r="AK13" s="32">
-        <f>12201000/(($E$11)*0.5665)</f>
-        <v>160062.77891805803</v>
-      </c>
-      <c r="AL13" s="32">
-        <f>1420000/(($E$11)*0.5913)</f>
-        <v>17847.414292623114</v>
-      </c>
-      <c r="AM13" s="32">
-        <f>1060000/(($E$11)*0.5665)</f>
-        <v>13905.954073694083</v>
-      </c>
-      <c r="AN13" s="65">
+      <c r="AI13">
+        <f>30074.264/($E$11/1049.5)</f>
+        <v>234569.90412902998</v>
+      </c>
+      <c r="AJ13">
+        <f>15217708/(($E$11)*0.5913)</f>
+        <v>191265.30933814443</v>
+      </c>
+      <c r="AK13">
+        <f>10200036/(($E$11)*0.5665)</f>
+        <v>133812.48317549651</v>
+      </c>
+      <c r="AL13">
+        <f>1187120/(($E$11)*0.5913)</f>
+        <v>14920.438348632922</v>
+      </c>
+      <c r="AM13">
+        <f>886160/(($E$11)*0.5665)</f>
+        <v>11625.377605608253</v>
+      </c>
+      <c r="AN13" s="61">
         <f t="shared" si="9"/>
-        <v>775285.45707343332</v>
-      </c>
-    </row>
-    <row r="14" spans="3:40" x14ac:dyDescent="0.3">
+        <v>660290.55747308198</v>
+      </c>
+    </row>
+    <row r="14" spans="3:40" ht="15">
       <c r="AC14" s="2" t="s">
         <v>27</v>
       </c>
@@ -5551,32 +5998,32 @@
         <f>9000/($E$12/1049.5)</f>
         <v>68810.774054367997</v>
       </c>
-      <c r="AI14" s="32">
-        <f>34890/($E$12/1049.5)</f>
-        <v>266756.43408409995</v>
-      </c>
-      <c r="AJ14" s="32">
-        <f>21665000/(($E$12)*0.5913)</f>
-        <v>266920.73082885414</v>
-      </c>
-      <c r="AK14" s="32">
-        <f>12085000/(($E$12)*0.5665)</f>
-        <v>155409.73913420385</v>
-      </c>
-      <c r="AL14" s="32">
-        <f>1130000/(($E$12)*0.5913)</f>
-        <v>13922.013655047551</v>
-      </c>
-      <c r="AM14" s="32">
-        <f>531000/(($E$12)*0.5665)</f>
-        <v>6828.5123277006414</v>
-      </c>
-      <c r="AN14" s="65">
+      <c r="AI14">
+        <f>26725.74/($E$12/1049.5)</f>
+        <v>204335.42850842059</v>
+      </c>
+      <c r="AJ14">
+        <f>16595390/(($E$12)*0.5913)</f>
+        <v>204461.27981490226</v>
+      </c>
+      <c r="AK14">
+        <f>9257110/(($E$12)*0.5665)</f>
+        <v>119043.86017680015</v>
+      </c>
+      <c r="AL14">
+        <f>865580/(($E$12)*0.5913)</f>
+        <v>10664.262459766423</v>
+      </c>
+      <c r="AM14">
+        <f>406746/(($E$12)*0.5665)</f>
+        <v>5230.6404430186913</v>
+      </c>
+      <c r="AN14" s="61">
         <f t="shared" si="9"/>
-        <v>778648.20408427413</v>
-      </c>
-    </row>
-    <row r="15" spans="3:40" x14ac:dyDescent="0.3">
+        <v>612546.24545727612</v>
+      </c>
+    </row>
+    <row r="15" spans="3:40" ht="15">
       <c r="AC15" s="2" t="s">
         <v>28</v>
       </c>
@@ -5592,61 +6039,70 @@
         <f>$E$13/1049.5</f>
         <v>0.12858498153742104</v>
       </c>
-      <c r="AH15" s="71">
+      <c r="AH15" s="65">
         <f>9000/($E$13/1049.5)</f>
         <v>69992.621940695331</v>
       </c>
-      <c r="AI15" s="67">
-        <f>35700/($E$13/1049.5)</f>
-        <v>277637.40036475816</v>
-      </c>
-      <c r="AJ15" s="67">
-        <f>20857000/(($E$13)*0.5913)</f>
-        <v>261379.349251723</v>
-      </c>
-      <c r="AK15" s="67">
-        <f>13666000/(($E$13)*0.5665)</f>
-        <v>178759.36877090493</v>
-      </c>
-      <c r="AL15" s="67">
-        <f>970000/(($E$13)*0.5913)</f>
-        <v>12156.013270085406</v>
-      </c>
-      <c r="AM15" s="67">
-        <f>351000/(($E$13)*0.5665)</f>
-        <v>4591.2877534456047</v>
-      </c>
-      <c r="AN15" s="69">
+      <c r="AI15">
+        <f>26025.3/($E$13/1049.5)</f>
+        <v>202397.66486590868</v>
+      </c>
+      <c r="AJ15">
+        <f>15204753/(($E$13)*0.5913)</f>
+        <v>190545.54560450607</v>
+      </c>
+      <c r="AK15">
+        <f>9962514/(($E$13)*0.5665)</f>
+        <v>130315.57983398969</v>
+      </c>
+      <c r="AL15">
+        <f>707130/(($E$13)*0.5913)</f>
+        <v>8861.7336738922604</v>
+      </c>
+      <c r="AM15">
+        <f>255879/(($E$13)*0.5665)</f>
+        <v>3347.0487722618454</v>
+      </c>
+      <c r="AN15" s="62">
         <f t="shared" si="9"/>
-        <v>804516.04135161242</v>
-      </c>
-    </row>
-    <row r="16" spans="3:40" x14ac:dyDescent="0.3">
-      <c r="L16" s="83" t="s">
-        <v>87</v>
-      </c>
-      <c r="M16" s="83"/>
-      <c r="N16" s="79"/>
-      <c r="O16" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="P16" s="79"/>
-      <c r="Q16" s="79"/>
-      <c r="R16" s="79"/>
-      <c r="S16" s="79"/>
-      <c r="T16" s="79"/>
-    </row>
-    <row r="17" spans="10:39" ht="57.6" x14ac:dyDescent="0.3">
+        <v>605460.19469125383</v>
+      </c>
+    </row>
+    <row r="16" spans="3:40">
+      <c r="G16">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="L16" s="89" t="s">
+        <v>117</v>
+      </c>
+      <c r="M16" s="89"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="85" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="85"/>
+      <c r="Q16" s="85"/>
+      <c r="R16" s="85"/>
+      <c r="S16" s="85"/>
+      <c r="T16" s="85"/>
+    </row>
+    <row r="17" spans="7:30" ht="57.75">
+      <c r="G17" s="83">
+        <v>0.93400000000000005</v>
+      </c>
       <c r="J17" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="L17" s="84" t="s">
-        <v>90</v>
-      </c>
-      <c r="M17" s="84"/>
-      <c r="N17" s="80"/>
-    </row>
-    <row r="18" spans="10:39" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+      <c r="L17" s="90" t="s">
+        <v>120</v>
+      </c>
+      <c r="M17" s="90"/>
+      <c r="N17" s="86"/>
+    </row>
+    <row r="18" spans="7:30" ht="15">
+      <c r="G18" s="83">
+        <v>0.88500000000000001</v>
+      </c>
       <c r="X18" s="35"/>
       <c r="Y18" s="35"/>
       <c r="Z18" s="35"/>
@@ -5654,27 +6110,33 @@
       <c r="AB18" s="35"/>
       <c r="AC18" s="35"/>
     </row>
-    <row r="19" spans="10:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="7:30" ht="15">
+      <c r="G19" s="83">
+        <v>0.85</v>
+      </c>
       <c r="T19" s="39" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="U19" s="40" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="V19" s="40" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="W19" s="40" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="X19" s="39" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="Y19" s="39"/>
     </row>
-    <row r="20" spans="10:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="7:30" ht="15">
+      <c r="G20" s="83">
+        <v>0.876</v>
+      </c>
       <c r="T20" s="42" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="U20" s="44">
         <v>1022</v>
@@ -5686,21 +6148,16 @@
         <v>1635</v>
       </c>
       <c r="X20" s="41" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="Y20" s="41"/>
-      <c r="AF20" s="12"/>
-      <c r="AG20" s="12"/>
-      <c r="AH20" s="12"/>
-      <c r="AI20" s="12"/>
-      <c r="AJ20" s="12"/>
-      <c r="AK20" s="12"/>
-      <c r="AL20" s="12"/>
-      <c r="AM20" s="12"/>
-    </row>
-    <row r="21" spans="10:39" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="7:30" ht="15">
+      <c r="G21" s="83">
+        <v>0.83599999999999997</v>
+      </c>
       <c r="T21" s="42" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="U21" s="44">
         <v>1257</v>
@@ -5712,13 +6169,16 @@
         <v>1914</v>
       </c>
       <c r="X21" s="41" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="Y21" s="41"/>
     </row>
-    <row r="22" spans="10:39" x14ac:dyDescent="0.3">
+    <row r="22" spans="7:30" ht="15">
+      <c r="G22" s="83">
+        <v>0.76600000000000001</v>
+      </c>
       <c r="T22" s="42" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="U22" s="44">
         <v>1137</v>
@@ -5730,13 +6190,16 @@
         <v>2700</v>
       </c>
       <c r="X22" s="41" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="Y22" s="41"/>
     </row>
-    <row r="23" spans="10:39" x14ac:dyDescent="0.3">
+    <row r="23" spans="7:30" ht="15">
+      <c r="G23" s="83">
+        <v>0.72899999999999998</v>
+      </c>
       <c r="T23" s="42" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="U23" s="40">
         <v>616</v>
@@ -5748,24 +6211,24 @@
         <v>1630</v>
       </c>
       <c r="X23" s="41" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="Y23" s="41"/>
     </row>
-    <row r="24" spans="10:39" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="7:30" ht="57.75">
       <c r="O24" s="31" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="P24" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="Q24" s="36" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="R24" s="36"/>
       <c r="S24" s="36"/>
       <c r="T24" s="42" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="U24" s="44">
         <v>1480</v>
@@ -5777,29 +6240,29 @@
         <v>2610</v>
       </c>
       <c r="X24" s="41" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="Y24" s="41"/>
-      <c r="Z24" s="49"/>
+      <c r="Z24" s="87"/>
       <c r="AA24" s="39" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="AB24" s="40" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="AC24" s="40" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="AD24" s="40" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="25" spans="10:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="O25" s="54">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="7:30" ht="15.6">
+      <c r="O25" s="53">
         <v>2042771015.5999999</v>
       </c>
-      <c r="P25" s="56">
-        <f>(Sheet1!M34*1000)/'Açúcar e Etanol'!O25</f>
+      <c r="P25" s="55">
+        <f>('Base Geral'!M34*1000)/'Açúcar e Etanol'!O25</f>
         <v>0.30372243793451642</v>
       </c>
       <c r="Q25" s="36">
@@ -5808,7 +6271,7 @@
       <c r="R25" s="36"/>
       <c r="S25" s="36"/>
       <c r="T25" s="42" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="U25" s="44">
         <v>1060</v>
@@ -5820,11 +6283,11 @@
         <v>2480</v>
       </c>
       <c r="X25" s="41" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="Y25" s="41"/>
       <c r="AA25" s="41" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="AB25" s="43">
         <v>10100000</v>
@@ -5836,12 +6299,12 @@
         <v>30830000</v>
       </c>
     </row>
-    <row r="26" spans="10:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="O26" s="54">
+    <row r="26" spans="7:30" ht="15.6">
+      <c r="O26" s="53">
         <v>2072045104.5999999</v>
       </c>
-      <c r="P26" s="56">
-        <f>(Sheet1!M35*1000)/'Açúcar e Etanol'!O26</f>
+      <c r="P26" s="55">
+        <f>('Base Geral'!M35*1000)/'Açúcar e Etanol'!O26</f>
         <v>0.31018522259633635</v>
       </c>
       <c r="Q26" s="36">
@@ -5850,7 +6313,7 @@
       <c r="R26" s="36"/>
       <c r="S26" s="36"/>
       <c r="T26" s="42" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="U26" s="40">
         <v>531</v>
@@ -5862,11 +6325,11 @@
         <v>1670</v>
       </c>
       <c r="X26" s="41" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="Y26" s="41"/>
       <c r="AA26" s="41" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="AB26" s="43">
         <v>10305000</v>
@@ -5878,12 +6341,12 @@
         <v>32849000</v>
       </c>
     </row>
-    <row r="27" spans="10:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="O27" s="54">
+    <row r="27" spans="7:30" ht="15.6">
+      <c r="O27" s="53">
         <v>1990827165.9000001</v>
       </c>
-      <c r="P27" s="56">
-        <f>(Sheet1!M36*1000)/'Açúcar e Etanol'!O27</f>
+      <c r="P27" s="55">
+        <f>('Base Geral'!M36*1000)/'Açúcar e Etanol'!O27</f>
         <v>0.32766577238516875</v>
       </c>
       <c r="Q27" s="36">
@@ -5892,7 +6355,7 @@
       <c r="R27" s="36"/>
       <c r="S27" s="36"/>
       <c r="T27" s="42" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="U27" s="40">
         <v>351</v>
@@ -5904,11 +6367,11 @@
         <v>1322</v>
       </c>
       <c r="X27" s="41" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="Y27" s="41"/>
       <c r="AA27" s="41" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="AB27" s="43">
         <v>9670000</v>
@@ -5920,12 +6383,12 @@
         <v>28928000</v>
       </c>
     </row>
-    <row r="28" spans="10:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="O28" s="54">
+    <row r="28" spans="7:30" ht="15.6">
+      <c r="O28" s="53">
         <v>3964534614.3000002</v>
       </c>
-      <c r="P28" s="56">
-        <f>(Sheet1!M37*1000)/'Açúcar e Etanol'!O28</f>
+      <c r="P28" s="55">
+        <f>('Base Geral'!M37*1000)/'Açúcar e Etanol'!O28</f>
         <v>0.1476110432707945</v>
       </c>
       <c r="Q28" s="36">
@@ -5940,7 +6403,7 @@
       <c r="X28" s="29"/>
       <c r="Y28" s="29"/>
       <c r="AA28" s="41" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AB28" s="43">
         <v>10616000</v>
@@ -5952,12 +6415,12 @@
         <v>27408000</v>
       </c>
     </row>
-    <row r="29" spans="10:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="O29" s="54">
+    <row r="29" spans="7:30" ht="15.6">
+      <c r="O29" s="53">
         <v>2025064447.3</v>
       </c>
-      <c r="P29" s="56">
-        <f>(Sheet1!M38*1000)/'Açúcar e Etanol'!O29</f>
+      <c r="P29" s="55">
+        <f>('Base Geral'!M38*1000)/'Açúcar e Etanol'!O29</f>
         <v>0.30128985169014377</v>
       </c>
       <c r="Q29" s="36">
@@ -5972,7 +6435,7 @@
       <c r="X29" s="29"/>
       <c r="Y29" s="29"/>
       <c r="AA29" s="41" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="AB29" s="43">
         <v>11621000</v>
@@ -5984,12 +6447,12 @@
         <v>27150000</v>
       </c>
     </row>
-    <row r="30" spans="10:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="O30" s="55">
+    <row r="30" spans="7:30" ht="15.6">
+      <c r="O30" s="54">
         <v>2122451453</v>
       </c>
-      <c r="P30" s="56">
-        <f>(Sheet1!M39*1000)/'Açúcar e Etanol'!O30</f>
+      <c r="P30" s="55">
+        <f>('Base Geral'!M39*1000)/'Açúcar e Etanol'!O30</f>
         <v>0.33603318722831399</v>
       </c>
       <c r="Q30" s="36">
@@ -6004,7 +6467,7 @@
       <c r="X30" s="29"/>
       <c r="Y30" s="29"/>
       <c r="AA30" s="41" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="AB30" s="43">
         <v>12201000</v>
@@ -6016,12 +6479,12 @@
         <v>30404000</v>
       </c>
     </row>
-    <row r="31" spans="10:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="O31" s="54">
+    <row r="31" spans="7:30" ht="15.6">
+      <c r="O31" s="53">
         <v>2035253752.7</v>
       </c>
-      <c r="P31" s="56">
-        <f>(Sheet1!M40*1000)/'Açúcar e Etanol'!O31</f>
+      <c r="P31" s="55">
+        <f>('Base Geral'!M40*1000)/'Açúcar e Etanol'!O31</f>
         <v>0.33757886760406491</v>
       </c>
       <c r="Q31" s="36">
@@ -6036,7 +6499,7 @@
       <c r="X31" s="29"/>
       <c r="Y31" s="29"/>
       <c r="AA31" s="41" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AB31" s="43">
         <v>12085000</v>
@@ -6048,9 +6511,9 @@
         <v>33750000</v>
       </c>
     </row>
-    <row r="32" spans="10:39" x14ac:dyDescent="0.3">
+    <row r="32" spans="7:30">
       <c r="AA32" s="41" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="AB32" s="43">
         <v>13666000</v>
@@ -6062,47 +6525,47 @@
         <v>34523000</v>
       </c>
     </row>
-    <row r="46" spans="21:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="21:23">
       <c r="U46" s="39"/>
       <c r="V46" s="39"/>
       <c r="W46" s="39"/>
     </row>
-    <row r="47" spans="21:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="21:23">
       <c r="U47" s="42"/>
       <c r="V47" s="42"/>
       <c r="W47" s="41"/>
     </row>
-    <row r="48" spans="21:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="21:23">
       <c r="U48" s="42"/>
       <c r="V48" s="42"/>
       <c r="W48" s="41"/>
     </row>
-    <row r="49" spans="21:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="21:23">
       <c r="U49" s="42"/>
       <c r="V49" s="42"/>
       <c r="W49" s="41"/>
     </row>
-    <row r="50" spans="21:23" x14ac:dyDescent="0.3">
+    <row r="50" spans="21:23">
       <c r="U50" s="42"/>
       <c r="V50" s="42"/>
       <c r="W50" s="41"/>
     </row>
-    <row r="51" spans="21:23" x14ac:dyDescent="0.3">
+    <row r="51" spans="21:23">
       <c r="U51" s="42"/>
       <c r="V51" s="42"/>
       <c r="W51" s="41"/>
     </row>
-    <row r="52" spans="21:23" x14ac:dyDescent="0.3">
+    <row r="52" spans="21:23">
       <c r="U52" s="42"/>
       <c r="V52" s="42"/>
       <c r="W52" s="41"/>
     </row>
-    <row r="53" spans="21:23" x14ac:dyDescent="0.3">
+    <row r="53" spans="21:23">
       <c r="U53" s="42"/>
       <c r="V53" s="42"/>
       <c r="W53" s="41"/>
     </row>
-    <row r="54" spans="21:23" x14ac:dyDescent="0.3">
+    <row r="54" spans="21:23">
       <c r="U54" s="42"/>
       <c r="V54" s="42"/>
       <c r="W54" s="41"/>
